--- a/Dados/Bruto/PIB municipios.xlsx
+++ b/Dados/Bruto/PIB municipios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao-giorio\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao-giorio\Desktop\Painel PIB Municípios\Dados\Bruto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C76529D-3F82-4F85-86C6-B1DA5A303AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B144F4D2-F5E4-456A-A475-498228473408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1977,7 +1977,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1991,6 +1991,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2279,7 +2282,8 @@
     <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="26" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="18" bestFit="1" customWidth="1"/>
     <col min="27" max="33" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2372,15 +2376,19 @@
         <v>2026</v>
       </c>
       <c r="AD1" s="4">
+        <f>AC1+1</f>
         <v>2027</v>
       </c>
       <c r="AE1" s="4">
+        <f t="shared" ref="AE1:AG1" si="0">AD1+1</f>
         <v>2028</v>
       </c>
       <c r="AF1" s="4">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="AG1" s="4">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
     </row>
@@ -2457,10 +2465,10 @@
       <c r="X2" s="2">
         <v>88675841</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y2" s="7">
         <v>120866364.5</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z2" s="7">
         <v>115985000</v>
       </c>
       <c r="AA2" s="3">
@@ -2558,10 +2566,10 @@
       <c r="X3" s="2">
         <v>927593842</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="Y3" s="7">
         <v>1115883188.21</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="Z3" s="7">
         <v>1085858000</v>
       </c>
       <c r="AA3" s="3">
@@ -2659,32 +2667,32 @@
       <c r="X4" s="2">
         <v>467566745</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" s="7">
         <v>493080512.64999998</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z4" s="7">
         <v>496110000</v>
       </c>
       <c r="AA4" s="3">
-        <v>530401798.45249557</v>
+        <v>529158230.04611212</v>
       </c>
       <c r="AB4" s="3">
-        <v>539896795.94003439</v>
+        <v>540934307.75120389</v>
       </c>
       <c r="AC4" s="3">
-        <v>537502271.12507749</v>
+        <v>542507922.20667458</v>
       </c>
       <c r="AD4" s="3">
-        <v>549163258.43566251</v>
+        <v>556363362.54475617</v>
       </c>
       <c r="AE4" s="3">
-        <v>565003318.24308097</v>
+        <v>574017545.87883472</v>
       </c>
       <c r="AF4" s="3">
-        <v>578289898.16952109</v>
+        <v>589583110.11302912</v>
       </c>
       <c r="AG4" s="3">
-        <v>589986984.0216372</v>
+        <v>603891367.62585926</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -2760,32 +2768,32 @@
       <c r="X5" s="2">
         <v>274879646</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y5" s="7">
         <v>257214763.78999999</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="Z5" s="7">
         <v>279406000</v>
       </c>
       <c r="AA5" s="3">
-        <v>292820725.11795992</v>
+        <v>291210745.19219226</v>
       </c>
       <c r="AB5" s="3">
-        <v>299558670.36927283</v>
+        <v>298448970.96952605</v>
       </c>
       <c r="AC5" s="3">
-        <v>303185620.24141264</v>
+        <v>303603271.62592012</v>
       </c>
       <c r="AD5" s="3">
-        <v>310723426.19141024</v>
+        <v>311540609.26403445</v>
       </c>
       <c r="AE5" s="3">
-        <v>319532947.96377313</v>
+        <v>320441821.15135366</v>
       </c>
       <c r="AF5" s="3">
-        <v>327761225.51123351</v>
+        <v>329017559.79292399</v>
       </c>
       <c r="AG5" s="3">
-        <v>335675214.46500385</v>
+        <v>337455330.23327315</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -2861,10 +2869,10 @@
       <c r="X6" s="2">
         <v>768472811</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6" s="7">
         <v>827476468.38999999</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6" s="7">
         <v>747812000</v>
       </c>
       <c r="AA6" s="3">
@@ -2962,10 +2970,10 @@
       <c r="X7" s="2">
         <v>162533229</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7" s="7">
         <v>175114292.52000001</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="Z7" s="7">
         <v>240633000</v>
       </c>
       <c r="AA7" s="3">
@@ -3063,10 +3071,10 @@
       <c r="X8" s="2">
         <v>192474648</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="Y8" s="7">
         <v>226763438.68000001</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="Z8" s="7">
         <v>183332000</v>
       </c>
       <c r="AA8" s="3">
@@ -3164,10 +3172,10 @@
       <c r="X9" s="2">
         <v>235572682</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y9" s="7">
         <v>231629033.22999999</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z9" s="7">
         <v>281792000</v>
       </c>
       <c r="AA9" s="3">
@@ -3265,10 +3273,10 @@
       <c r="X10" s="2">
         <v>397128637</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y10" s="7">
         <v>385755861.42000002</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="Z10" s="7">
         <v>414787000</v>
       </c>
       <c r="AA10" s="3">
@@ -3366,10 +3374,10 @@
       <c r="X11" s="2">
         <v>93237635</v>
       </c>
-      <c r="Y11" s="2">
+      <c r="Y11" s="7">
         <v>89902294.909999996</v>
       </c>
-      <c r="Z11" s="2">
+      <c r="Z11" s="7">
         <v>94012000</v>
       </c>
       <c r="AA11" s="3">
@@ -3467,10 +3475,10 @@
       <c r="X12" s="2">
         <v>240547574</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y12" s="7">
         <v>242726445.33000001</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="Z12" s="7">
         <v>261385000</v>
       </c>
       <c r="AA12" s="3">
@@ -3568,10 +3576,10 @@
       <c r="X13" s="2">
         <v>206031379</v>
       </c>
-      <c r="Y13" s="2">
+      <c r="Y13" s="7">
         <v>161579152.91</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="Z13" s="7">
         <v>192262000</v>
       </c>
       <c r="AA13" s="3">
@@ -3669,10 +3677,10 @@
       <c r="X14" s="2">
         <v>273243774</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y14" s="7">
         <v>234677014.31999999</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="Z14" s="7">
         <v>251491000</v>
       </c>
       <c r="AA14" s="3">
@@ -3770,10 +3778,10 @@
       <c r="X15" s="2">
         <v>99814172</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y15" s="7">
         <v>103173393.02</v>
       </c>
-      <c r="Z15" s="2">
+      <c r="Z15" s="7">
         <v>117403000</v>
       </c>
       <c r="AA15" s="3">
@@ -3871,10 +3879,10 @@
       <c r="X16" s="2">
         <v>940131989</v>
       </c>
-      <c r="Y16" s="2">
+      <c r="Y16" s="7">
         <v>897233821.39999998</v>
       </c>
-      <c r="Z16" s="2">
+      <c r="Z16" s="7">
         <v>1163092000</v>
       </c>
       <c r="AA16" s="3">
@@ -3972,32 +3980,32 @@
       <c r="X17" s="2">
         <v>522228011</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y17" s="7">
         <v>529940048.19</v>
       </c>
-      <c r="Z17" s="2">
+      <c r="Z17" s="7">
         <v>510610000</v>
       </c>
       <c r="AA17" s="3">
-        <v>534449487.9629494</v>
+        <v>534194042.83771771</v>
       </c>
       <c r="AB17" s="3">
-        <v>534264054.00129974</v>
+        <v>536203260.59598678</v>
       </c>
       <c r="AC17" s="3">
-        <v>523119978.11712283</v>
+        <v>528299169.94826621</v>
       </c>
       <c r="AD17" s="3">
-        <v>524760681.9142164</v>
+        <v>531946158.45191759</v>
       </c>
       <c r="AE17" s="3">
-        <v>529851656.3536225</v>
+        <v>538768450.52538443</v>
       </c>
       <c r="AF17" s="3">
-        <v>532399584.53300887</v>
+        <v>543300453.6043216</v>
       </c>
       <c r="AG17" s="3">
-        <v>533351810.1028626</v>
+        <v>546390472.20687473</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -4073,10 +4081,10 @@
       <c r="X18" s="2">
         <v>335689006</v>
       </c>
-      <c r="Y18" s="2">
+      <c r="Y18" s="7">
         <v>379928323.16000003</v>
       </c>
-      <c r="Z18" s="2">
+      <c r="Z18" s="7">
         <v>400561000</v>
       </c>
       <c r="AA18" s="3">
@@ -4174,32 +4182,32 @@
       <c r="X19" s="2">
         <v>8837959013</v>
       </c>
-      <c r="Y19" s="2">
+      <c r="Y19" s="7">
         <v>8749373247.8400002</v>
       </c>
-      <c r="Z19" s="2">
+      <c r="Z19" s="7">
         <v>9900040000</v>
       </c>
       <c r="AA19" s="3">
-        <v>11202738827.3379</v>
+        <v>11203948131.492479</v>
       </c>
       <c r="AB19" s="3">
-        <v>12671982889.991663</v>
+        <v>12673475320.890568</v>
       </c>
       <c r="AC19" s="3">
-        <v>14331516310.581169</v>
+        <v>14332731368.270733</v>
       </c>
       <c r="AD19" s="3">
-        <v>16211562353.767696</v>
+        <v>16213213967.593256</v>
       </c>
       <c r="AE19" s="3">
-        <v>18339221592.1688</v>
+        <v>18341654774.712593</v>
       </c>
       <c r="AF19" s="3">
-        <v>20745292467.687088</v>
+        <v>20748471977.124168</v>
       </c>
       <c r="AG19" s="3">
-        <v>23466456093.431252</v>
+        <v>23470387868.46756</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -4275,10 +4283,10 @@
       <c r="X20" s="2">
         <v>2815293602</v>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y20" s="7">
         <v>2951336425.79</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="Z20" s="7">
         <v>3023100000</v>
       </c>
       <c r="AA20" s="3">
@@ -4376,10 +4384,10 @@
       <c r="X21" s="2">
         <v>321162083</v>
       </c>
-      <c r="Y21" s="2">
+      <c r="Y21" s="7">
         <v>313560780.88999999</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="Z21" s="7">
         <v>343668000</v>
       </c>
       <c r="AA21" s="3">
@@ -4477,10 +4485,10 @@
       <c r="X22" s="2">
         <v>148660183</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y22" s="7">
         <v>150151962.84</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="Z22" s="7">
         <v>154297000</v>
       </c>
       <c r="AA22" s="3">
@@ -4578,10 +4586,10 @@
       <c r="X23" s="2">
         <v>240626653</v>
       </c>
-      <c r="Y23" s="2">
+      <c r="Y23" s="7">
         <v>201777005.62</v>
       </c>
-      <c r="Z23" s="2">
+      <c r="Z23" s="7">
         <v>194588000</v>
       </c>
       <c r="AA23" s="3">
@@ -4679,32 +4687,32 @@
       <c r="X24" s="2">
         <v>289158709</v>
       </c>
-      <c r="Y24" s="2">
+      <c r="Y24" s="7">
         <v>301873931.75</v>
       </c>
-      <c r="Z24" s="2">
+      <c r="Z24" s="7">
         <v>315202000</v>
       </c>
       <c r="AA24" s="3">
-        <v>321291109.05182153</v>
+        <v>320477917.87885356</v>
       </c>
       <c r="AB24" s="3">
-        <v>325283806.42788231</v>
+        <v>324603924.3570385</v>
       </c>
       <c r="AC24" s="3">
-        <v>328348591.96761924</v>
+        <v>328236118.4778769</v>
       </c>
       <c r="AD24" s="3">
-        <v>332596562.67123991</v>
+        <v>332555928.56689721</v>
       </c>
       <c r="AE24" s="3">
-        <v>337219399.21555954</v>
+        <v>337111933.62102371</v>
       </c>
       <c r="AF24" s="3">
-        <v>341664759.74373066</v>
+        <v>341594866.54718846</v>
       </c>
       <c r="AG24" s="3">
-        <v>346017538.69494778</v>
+        <v>346052666.75025046</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
@@ -4780,32 +4788,32 @@
       <c r="X25" s="2">
         <v>148693231</v>
       </c>
-      <c r="Y25" s="2">
+      <c r="Y25" s="7">
         <v>153604223.22999999</v>
       </c>
-      <c r="Z25" s="2">
+      <c r="Z25" s="7">
         <v>146755000</v>
       </c>
       <c r="AA25" s="3">
-        <v>148446765.03068179</v>
+        <v>148987692.35634306</v>
       </c>
       <c r="AB25" s="3">
-        <v>149854798.17601171</v>
+        <v>150461459.89099607</v>
       </c>
       <c r="AC25" s="3">
-        <v>151142693.70110267</v>
+        <v>151600609.6740258</v>
       </c>
       <c r="AD25" s="3">
-        <v>152599162.83938137</v>
+        <v>153159973.88003084</v>
       </c>
       <c r="AE25" s="3">
-        <v>154113176.18509296</v>
+        <v>154849148.21895245</v>
       </c>
       <c r="AF25" s="3">
-        <v>155609463.33472607</v>
+        <v>156471227.97342247</v>
       </c>
       <c r="AG25" s="3">
-        <v>157099867.32139337</v>
+        <v>158056829.2271696</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
@@ -4881,32 +4889,32 @@
       <c r="X26" s="2">
         <v>480278393</v>
       </c>
-      <c r="Y26" s="2">
+      <c r="Y26" s="7">
         <v>447341075.33999997</v>
       </c>
-      <c r="Z26" s="2">
+      <c r="Z26" s="7">
         <v>468008000</v>
       </c>
       <c r="AA26" s="3">
-        <v>509483224.11075252</v>
+        <v>508197038.97342706</v>
       </c>
       <c r="AB26" s="3">
-        <v>532762839.53293884</v>
+        <v>533251619.8236233</v>
       </c>
       <c r="AC26" s="3">
-        <v>547132460.05962455</v>
+        <v>551036759.73172629</v>
       </c>
       <c r="AD26" s="3">
-        <v>573871801.08172917</v>
+        <v>579695822.40901363</v>
       </c>
       <c r="AE26" s="3">
-        <v>605356509.72056484</v>
+        <v>612804560.85584092</v>
       </c>
       <c r="AF26" s="3">
-        <v>635865347.72275162</v>
+        <v>645472977.61944842</v>
       </c>
       <c r="AG26" s="3">
-        <v>666159022.3718344</v>
+        <v>678367159.95143461</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
@@ -4982,10 +4990,10 @@
       <c r="X27" s="2">
         <v>261913057</v>
       </c>
-      <c r="Y27" s="2">
+      <c r="Y27" s="7">
         <v>275981430.98000002</v>
       </c>
-      <c r="Z27" s="2">
+      <c r="Z27" s="7">
         <v>302101000</v>
       </c>
       <c r="AA27" s="3">
@@ -5083,32 +5091,32 @@
       <c r="X28" s="2">
         <v>300546080</v>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y28" s="7">
         <v>309132333.88</v>
       </c>
-      <c r="Z28" s="2">
+      <c r="Z28" s="7">
         <v>321609000</v>
       </c>
       <c r="AA28" s="3">
-        <v>330203978.02710986</v>
+        <v>330149718.16880262</v>
       </c>
       <c r="AB28" s="3">
-        <v>341795173.13111305</v>
+        <v>341683420.73741162</v>
       </c>
       <c r="AC28" s="3">
-        <v>355042067.80662704</v>
+        <v>354868505.43073589</v>
       </c>
       <c r="AD28" s="3">
-        <v>367284863.03291088</v>
+        <v>367045556.986682</v>
       </c>
       <c r="AE28" s="3">
-        <v>379520311.10955036</v>
+        <v>379211206.12034631</v>
       </c>
       <c r="AF28" s="3">
-        <v>392494124.44633955</v>
+        <v>392110590.14770478</v>
       </c>
       <c r="AG28" s="3">
-        <v>406122597.55855578</v>
+        <v>405659719.50900751</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
@@ -5184,32 +5192,32 @@
       <c r="X29" s="2">
         <v>8685311833</v>
       </c>
-      <c r="Y29" s="2">
+      <c r="Y29" s="7">
         <v>8744391518.8600006</v>
       </c>
-      <c r="Z29" s="2">
+      <c r="Z29" s="7">
         <v>9004373000</v>
       </c>
       <c r="AA29" s="3">
-        <v>9449956228.1673584</v>
+        <v>9442876541.4399719</v>
       </c>
       <c r="AB29" s="3">
-        <v>9763679563.6788921</v>
+        <v>9769441111.9484215</v>
       </c>
       <c r="AC29" s="3">
-        <v>10018470664.602221</v>
+        <v>10047160482.19437</v>
       </c>
       <c r="AD29" s="3">
-        <v>10363151766.148911</v>
+        <v>10405126305.897335</v>
       </c>
       <c r="AE29" s="3">
-        <v>10743250017.785408</v>
+        <v>10796346838.545567</v>
       </c>
       <c r="AF29" s="3">
-        <v>11119088157.318314</v>
+        <v>11186423761.402039</v>
       </c>
       <c r="AG29" s="3">
-        <v>11496446131.766325</v>
+        <v>11580455007.163372</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
@@ -5285,10 +5293,10 @@
       <c r="X30" s="2">
         <v>256115507</v>
       </c>
-      <c r="Y30" s="2">
+      <c r="Y30" s="7">
         <v>283657259.70999998</v>
       </c>
-      <c r="Z30" s="2">
+      <c r="Z30" s="7">
         <v>308869000</v>
       </c>
       <c r="AA30" s="3">
@@ -5386,32 +5394,32 @@
       <c r="X31" s="2">
         <v>1786885889</v>
       </c>
-      <c r="Y31" s="2">
+      <c r="Y31" s="7">
         <v>1739481275.0799999</v>
       </c>
-      <c r="Z31" s="2">
+      <c r="Z31" s="7">
         <v>2097521000</v>
       </c>
       <c r="AA31" s="3">
-        <v>2309744677.8556685</v>
+        <v>2290226422.6830482</v>
       </c>
       <c r="AB31" s="3">
-        <v>2485836738.9835172</v>
+        <v>2468544051.8929162</v>
       </c>
       <c r="AC31" s="3">
-        <v>2648317873.9446073</v>
+        <v>2645660644.5506492</v>
       </c>
       <c r="AD31" s="3">
-        <v>2855113726.0049348</v>
+        <v>2854398020.2840662</v>
       </c>
       <c r="AE31" s="3">
-        <v>3087996163.5477486</v>
+        <v>3085187214.4921808</v>
       </c>
       <c r="AF31" s="3">
-        <v>3331862891.2895641</v>
+        <v>3330139504.9405212</v>
       </c>
       <c r="AG31" s="3">
-        <v>3589652706.6962471</v>
+        <v>3591543709.9380507</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
@@ -5487,32 +5495,32 @@
       <c r="X32" s="2">
         <v>347889591</v>
       </c>
-      <c r="Y32" s="2">
+      <c r="Y32" s="7">
         <v>388455439.19999999</v>
       </c>
-      <c r="Z32" s="2">
+      <c r="Z32" s="7">
         <v>420208000</v>
       </c>
       <c r="AA32" s="3">
-        <v>445462279.31622076</v>
+        <v>436335375.11808568</v>
       </c>
       <c r="AB32" s="3">
-        <v>459547624.28167099</v>
+        <v>444201254.5287472</v>
       </c>
       <c r="AC32" s="3">
-        <v>468488973.55443132</v>
+        <v>448266404.67289454</v>
       </c>
       <c r="AD32" s="3">
-        <v>485029633.52043408</v>
+        <v>457023020.35358304</v>
       </c>
       <c r="AE32" s="3">
-        <v>504542016.9972353</v>
+        <v>467248986.56895304</v>
       </c>
       <c r="AF32" s="3">
-        <v>523708037.8009851</v>
+        <v>476714538.11579621</v>
       </c>
       <c r="AG32" s="3">
-        <v>543049460.06505084</v>
+        <v>485748845.73062176</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
@@ -5588,10 +5596,10 @@
       <c r="X33" s="2">
         <v>120639085</v>
       </c>
-      <c r="Y33" s="2">
+      <c r="Y33" s="7">
         <v>118781422.72</v>
       </c>
-      <c r="Z33" s="2">
+      <c r="Z33" s="7">
         <v>130220000</v>
       </c>
       <c r="AA33" s="3">
@@ -5689,10 +5697,10 @@
       <c r="X34" s="2">
         <v>61706375</v>
       </c>
-      <c r="Y34" s="2">
+      <c r="Y34" s="7">
         <v>61149161.990000002</v>
       </c>
-      <c r="Z34" s="2">
+      <c r="Z34" s="7">
         <v>66206000</v>
       </c>
       <c r="AA34" s="3">
@@ -5790,32 +5798,32 @@
       <c r="X35" s="2">
         <v>2800156473</v>
       </c>
-      <c r="Y35" s="2">
+      <c r="Y35" s="7">
         <v>2798515562.1799998</v>
       </c>
-      <c r="Z35" s="2">
+      <c r="Z35" s="7">
         <v>2468505000</v>
       </c>
       <c r="AA35" s="3">
-        <v>2747657908.3497252</v>
+        <v>2772670453.5592885</v>
       </c>
       <c r="AB35" s="3">
-        <v>2927321288.2916155</v>
+        <v>2967337448.7943401</v>
       </c>
       <c r="AC35" s="3">
-        <v>3057841804.8467994</v>
+        <v>3107075817.8994746</v>
       </c>
       <c r="AD35" s="3">
-        <v>3268589042.2029438</v>
+        <v>3337418822.2586799</v>
       </c>
       <c r="AE35" s="3">
-        <v>3515622138.5571961</v>
+        <v>3609531829.9499054</v>
       </c>
       <c r="AF35" s="3">
-        <v>3763882003.7035069</v>
+        <v>3883927606.9192567</v>
       </c>
       <c r="AG35" s="3">
-        <v>4018145164.3546028</v>
+        <v>4165962746.4704332</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
@@ -5891,32 +5899,32 @@
       <c r="X36" s="2">
         <v>232335165</v>
       </c>
-      <c r="Y36" s="2">
+      <c r="Y36" s="7">
         <v>231714490.63999999</v>
       </c>
-      <c r="Z36" s="2">
+      <c r="Z36" s="7">
         <v>277735000</v>
       </c>
       <c r="AA36" s="3">
-        <v>281834310.76130056</v>
+        <v>281109904.86330312</v>
       </c>
       <c r="AB36" s="3">
-        <v>282324447.55890036</v>
+        <v>281655424.48496193</v>
       </c>
       <c r="AC36" s="3">
-        <v>281212328.30860484</v>
+        <v>280947811.04434752</v>
       </c>
       <c r="AD36" s="3">
-        <v>281972553.52259481</v>
+        <v>281705469.90100569</v>
       </c>
       <c r="AE36" s="3">
-        <v>283247295.8245405</v>
+        <v>282866668.18767405</v>
       </c>
       <c r="AF36" s="3">
-        <v>284144154.984083</v>
+        <v>283732198.91691172</v>
       </c>
       <c r="AG36" s="3">
-        <v>284806286.97994077</v>
+        <v>284414346.2089082</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
@@ -5992,10 +6000,10 @@
       <c r="X37" s="2">
         <v>68045675</v>
       </c>
-      <c r="Y37" s="2">
+      <c r="Y37" s="7">
         <v>80767116.489999995</v>
       </c>
-      <c r="Z37" s="2">
+      <c r="Z37" s="7">
         <v>86050000</v>
       </c>
       <c r="AA37" s="3">
@@ -6093,32 +6101,32 @@
       <c r="X38" s="2">
         <v>554921850</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y38" s="7">
         <v>506937760.98000002</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="Z38" s="7">
         <v>496824000</v>
       </c>
       <c r="AA38" s="3">
-        <v>515747612.83109391</v>
+        <v>516847496.55111271</v>
       </c>
       <c r="AB38" s="3">
-        <v>528387141.0359661</v>
+        <v>530202178.24074328</v>
       </c>
       <c r="AC38" s="3">
-        <v>538206782.3444761</v>
+        <v>540557527.72165346</v>
       </c>
       <c r="AD38" s="3">
-        <v>551938080.65949166</v>
+        <v>555103890.61132932</v>
       </c>
       <c r="AE38" s="3">
-        <v>567066048.45347142</v>
+        <v>571162400.12260175</v>
       </c>
       <c r="AF38" s="3">
-        <v>581807481.32743037</v>
+        <v>586826080.48133528</v>
       </c>
       <c r="AG38" s="3">
-        <v>596424726.57704401</v>
+        <v>602374296.76070833</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
@@ -6194,10 +6202,10 @@
       <c r="X39" s="2">
         <v>3151683696</v>
       </c>
-      <c r="Y39" s="2">
+      <c r="Y39" s="7">
         <v>3254858151.77</v>
       </c>
-      <c r="Z39" s="2">
+      <c r="Z39" s="7">
         <v>3523318000</v>
       </c>
       <c r="AA39" s="3">
@@ -6295,32 +6303,32 @@
       <c r="X40" s="2">
         <v>24289621944</v>
       </c>
-      <c r="Y40" s="2">
+      <c r="Y40" s="7">
         <v>24970315572.75</v>
       </c>
-      <c r="Z40" s="2">
+      <c r="Z40" s="7">
         <v>24871920000</v>
       </c>
       <c r="AA40" s="3">
-        <v>25855347808.80125</v>
+        <v>25818806860.959705</v>
       </c>
       <c r="AB40" s="3">
-        <v>26013795720.473335</v>
+        <v>26050605193.445381</v>
       </c>
       <c r="AC40" s="3">
-        <v>25794179838.72184</v>
+        <v>25953977318.349815</v>
       </c>
       <c r="AD40" s="3">
-        <v>26016077794.773296</v>
+        <v>26242908293.309048</v>
       </c>
       <c r="AE40" s="3">
-        <v>26361211675.296936</v>
+        <v>26641620995.864147</v>
       </c>
       <c r="AF40" s="3">
-        <v>26619303966.408127</v>
+        <v>26965765549.796726</v>
       </c>
       <c r="AG40" s="3">
-        <v>26822814092.379166</v>
+        <v>27243479647.753235</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
@@ -6396,10 +6404,10 @@
       <c r="X41" s="2">
         <v>160398097</v>
       </c>
-      <c r="Y41" s="2">
+      <c r="Y41" s="7">
         <v>144414264.43000001</v>
       </c>
-      <c r="Z41" s="2">
+      <c r="Z41" s="7">
         <v>145084000</v>
       </c>
       <c r="AA41" s="3">
@@ -6497,10 +6505,10 @@
       <c r="X42" s="2">
         <v>438661615</v>
       </c>
-      <c r="Y42" s="2">
+      <c r="Y42" s="7">
         <v>296656647.07999998</v>
       </c>
-      <c r="Z42" s="2">
+      <c r="Z42" s="7">
         <v>338788000</v>
       </c>
       <c r="AA42" s="3">
@@ -6598,10 +6606,10 @@
       <c r="X43" s="2">
         <v>187732271</v>
       </c>
-      <c r="Y43" s="2">
+      <c r="Y43" s="7">
         <v>197499752.5</v>
       </c>
-      <c r="Z43" s="2">
+      <c r="Z43" s="7">
         <v>187852000</v>
       </c>
       <c r="AA43" s="3">
@@ -6699,10 +6707,10 @@
       <c r="X44" s="2">
         <v>86989217</v>
       </c>
-      <c r="Y44" s="2">
+      <c r="Y44" s="7">
         <v>91793314.090000004</v>
       </c>
-      <c r="Z44" s="2">
+      <c r="Z44" s="7">
         <v>103572000</v>
       </c>
       <c r="AA44" s="3">
@@ -6800,10 +6808,10 @@
       <c r="X45" s="2">
         <v>498507864</v>
       </c>
-      <c r="Y45" s="2">
+      <c r="Y45" s="7">
         <v>457268378.24000001</v>
       </c>
-      <c r="Z45" s="2">
+      <c r="Z45" s="7">
         <v>454470000</v>
       </c>
       <c r="AA45" s="3">
@@ -6901,32 +6909,32 @@
       <c r="X46" s="2">
         <v>1035809268</v>
       </c>
-      <c r="Y46" s="2">
+      <c r="Y46" s="7">
         <v>1058298038.62</v>
       </c>
-      <c r="Z46" s="2">
+      <c r="Z46" s="7">
         <v>1178868000</v>
       </c>
       <c r="AA46" s="3">
-        <v>1231757265.8858905</v>
+        <v>1227310914.2358563</v>
       </c>
       <c r="AB46" s="3">
-        <v>1292492351.8986161</v>
+        <v>1287061787.3220124</v>
       </c>
       <c r="AC46" s="3">
-        <v>1358726558.7849715</v>
+        <v>1353982632.7229671</v>
       </c>
       <c r="AD46" s="3">
-        <v>1425275106.6159644</v>
+        <v>1419139199.1633813</v>
       </c>
       <c r="AE46" s="3">
-        <v>1494199181.3395452</v>
+        <v>1485927470.4544115</v>
       </c>
       <c r="AF46" s="3">
-        <v>1567146933.5674419</v>
+        <v>1557032415.012028</v>
       </c>
       <c r="AG46" s="3">
-        <v>1644103158.0430636</v>
+        <v>1632298898.0762849</v>
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
@@ -7002,32 +7010,32 @@
       <c r="X47" s="2">
         <v>508278246</v>
       </c>
-      <c r="Y47" s="2">
+      <c r="Y47" s="7">
         <v>509348098.29000002</v>
       </c>
-      <c r="Z47" s="2">
+      <c r="Z47" s="7">
         <v>554189000</v>
       </c>
       <c r="AA47" s="3">
-        <v>607443224.36068857</v>
+        <v>605042848.77027631</v>
       </c>
       <c r="AB47" s="3">
-        <v>642528424.60738802</v>
+        <v>641869055.02462339</v>
       </c>
       <c r="AC47" s="3">
-        <v>668898482.70161319</v>
+        <v>672288107.46293938</v>
       </c>
       <c r="AD47" s="3">
-        <v>709432291.10880387</v>
+        <v>714745550.39044881</v>
       </c>
       <c r="AE47" s="3">
-        <v>756218383.73489225</v>
+        <v>762966750.03097594</v>
       </c>
       <c r="AF47" s="3">
-        <v>803074345.02669561</v>
+        <v>811989056.07470453</v>
       </c>
       <c r="AG47" s="3">
-        <v>850856727.84974968</v>
+        <v>862550203.24982417</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
@@ -7103,10 +7111,10 @@
       <c r="X48" s="2">
         <v>2059613878</v>
       </c>
-      <c r="Y48" s="2">
+      <c r="Y48" s="7">
         <v>2150301357.71</v>
       </c>
-      <c r="Z48" s="2">
+      <c r="Z48" s="7">
         <v>2195935000</v>
       </c>
       <c r="AA48" s="3">
@@ -7204,32 +7212,32 @@
       <c r="X49" s="2">
         <v>295248970</v>
       </c>
-      <c r="Y49" s="2">
+      <c r="Y49" s="7">
         <v>283792019.48000002</v>
       </c>
-      <c r="Z49" s="2">
+      <c r="Z49" s="7">
         <v>273816000</v>
       </c>
       <c r="AA49" s="3">
-        <v>293155292.23645192</v>
+        <v>292903130.87462491</v>
       </c>
       <c r="AB49" s="3">
-        <v>295735664.71004534</v>
+        <v>297058240.98831773</v>
       </c>
       <c r="AC49" s="3">
-        <v>290365045.4856292</v>
+        <v>294079689.05679327</v>
       </c>
       <c r="AD49" s="3">
-        <v>294250374.71458465</v>
+        <v>299460702.60172749</v>
       </c>
       <c r="AE49" s="3">
-        <v>300726991.59681034</v>
+        <v>307260908.17761683</v>
       </c>
       <c r="AF49" s="3">
-        <v>305412060.70006627</v>
+        <v>313489681.50318038</v>
       </c>
       <c r="AG49" s="3">
-        <v>308957636.74051881</v>
+        <v>318727087.10437125</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
@@ -7305,10 +7313,10 @@
       <c r="X50" s="2">
         <v>162830661</v>
       </c>
-      <c r="Y50" s="2">
+      <c r="Y50" s="7">
         <v>123832175</v>
       </c>
-      <c r="Z50" s="2">
+      <c r="Z50" s="7">
         <v>143766000</v>
       </c>
       <c r="AA50" s="3">
@@ -7406,32 +7414,32 @@
       <c r="X51" s="2">
         <v>10297419057</v>
       </c>
-      <c r="Y51" s="2">
+      <c r="Y51" s="7">
         <v>10867605067.620001</v>
       </c>
-      <c r="Z51" s="2">
+      <c r="Z51" s="7">
         <v>11071535000</v>
       </c>
       <c r="AA51" s="3">
-        <v>11860845306.431965</v>
+        <v>11833729852.549326</v>
       </c>
       <c r="AB51" s="3">
-        <v>12167072322.05855</v>
+        <v>12184825220.059116</v>
       </c>
       <c r="AC51" s="3">
-        <v>12239923496.277679</v>
+        <v>12338178730.920624</v>
       </c>
       <c r="AD51" s="3">
-        <v>12597157934.891336</v>
+        <v>12740035331.391066</v>
       </c>
       <c r="AE51" s="3">
-        <v>13044774780.253641</v>
+        <v>13224640852.426186</v>
       </c>
       <c r="AF51" s="3">
-        <v>13446591051.145947</v>
+        <v>13673789667.023226</v>
       </c>
       <c r="AG51" s="3">
-        <v>13821521356.061115</v>
+        <v>14103797830.469702</v>
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
@@ -7507,10 +7515,10 @@
       <c r="X52" s="2">
         <v>5551361889</v>
       </c>
-      <c r="Y52" s="2">
+      <c r="Y52" s="7">
         <v>5392676153.4300003</v>
       </c>
-      <c r="Z52" s="2">
+      <c r="Z52" s="7">
         <v>5375161000</v>
       </c>
       <c r="AA52" s="3">
@@ -7608,10 +7616,10 @@
       <c r="X53" s="2">
         <v>373884143</v>
       </c>
-      <c r="Y53" s="2">
+      <c r="Y53" s="7">
         <v>371760566.5</v>
       </c>
-      <c r="Z53" s="2">
+      <c r="Z53" s="7">
         <v>382027000</v>
       </c>
       <c r="AA53" s="3">
@@ -7709,10 +7717,10 @@
       <c r="X54" s="2">
         <v>115303025</v>
       </c>
-      <c r="Y54" s="2">
+      <c r="Y54" s="7">
         <v>115908738.89</v>
       </c>
-      <c r="Z54" s="2">
+      <c r="Z54" s="7">
         <v>135173000</v>
       </c>
       <c r="AA54" s="3">
@@ -7810,32 +7818,32 @@
       <c r="X55" s="2">
         <v>2646987609</v>
       </c>
-      <c r="Y55" s="2">
+      <c r="Y55" s="7">
         <v>2805752052.1599998</v>
       </c>
-      <c r="Z55" s="2">
+      <c r="Z55" s="7">
         <v>2703378000</v>
       </c>
       <c r="AA55" s="3">
-        <v>2905012015.8227501</v>
+        <v>2919178605.227035</v>
       </c>
       <c r="AB55" s="3">
-        <v>3067462500.838047</v>
+        <v>3088158194.0475059</v>
       </c>
       <c r="AC55" s="3">
-        <v>3214028875.9989982</v>
+        <v>3237371765.9003878</v>
       </c>
       <c r="AD55" s="3">
-        <v>3398202605.1750379</v>
+        <v>3430030553.4822702</v>
       </c>
       <c r="AE55" s="3">
-        <v>3601783293.7395272</v>
+        <v>3644658773.2212462</v>
       </c>
       <c r="AF55" s="3">
-        <v>3810566888.4788713</v>
+        <v>3864398777.3687286</v>
       </c>
       <c r="AG55" s="3">
-        <v>4026885943.1253691</v>
+        <v>4091942882.0522704</v>
       </c>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
@@ -7911,32 +7919,32 @@
       <c r="X56" s="2">
         <v>825847547</v>
       </c>
-      <c r="Y56" s="2">
+      <c r="Y56" s="7">
         <v>844376219.76999998</v>
       </c>
-      <c r="Z56" s="2">
+      <c r="Z56" s="7">
         <v>872665000</v>
       </c>
       <c r="AA56" s="3">
-        <v>908792111.52225482</v>
+        <v>908860459.9291625</v>
       </c>
       <c r="AB56" s="3">
-        <v>932868913.49875021</v>
+        <v>933207090.7892983</v>
       </c>
       <c r="AC56" s="3">
-        <v>951519787.23520017</v>
+        <v>952228061.47758412</v>
       </c>
       <c r="AD56" s="3">
-        <v>977778934.13864601</v>
+        <v>978772288.84766209</v>
       </c>
       <c r="AE56" s="3">
-        <v>1006797010.4698776</v>
+        <v>1008063194.285439</v>
       </c>
       <c r="AF56" s="3">
-        <v>1035115222.704439</v>
+        <v>1036690362.1063403</v>
       </c>
       <c r="AG56" s="3">
-        <v>1063239234.0207511</v>
+        <v>1065152690.5864731</v>
       </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
@@ -8012,10 +8020,10 @@
       <c r="X57" s="2">
         <v>393062562</v>
       </c>
-      <c r="Y57" s="2">
+      <c r="Y57" s="7">
         <v>334060699.72000003</v>
       </c>
-      <c r="Z57" s="2">
+      <c r="Z57" s="7">
         <v>401476000</v>
       </c>
       <c r="AA57" s="3">
@@ -8113,10 +8121,10 @@
       <c r="X58" s="2">
         <v>516762120</v>
       </c>
-      <c r="Y58" s="2">
+      <c r="Y58" s="7">
         <v>533645394</v>
       </c>
-      <c r="Z58" s="2">
+      <c r="Z58" s="7">
         <v>532119000</v>
       </c>
       <c r="AA58" s="3">
@@ -8214,10 +8222,10 @@
       <c r="X59" s="2">
         <v>3080948156</v>
       </c>
-      <c r="Y59" s="2">
+      <c r="Y59" s="7">
         <v>3537852568.73</v>
       </c>
-      <c r="Z59" s="2">
+      <c r="Z59" s="7">
         <v>3456854000</v>
       </c>
       <c r="AA59" s="3">
@@ -8315,10 +8323,10 @@
       <c r="X60" s="2">
         <v>348964829</v>
       </c>
-      <c r="Y60" s="2">
+      <c r="Y60" s="7">
         <v>398776065.32999998</v>
       </c>
-      <c r="Z60" s="2">
+      <c r="Z60" s="7">
         <v>412708000</v>
       </c>
       <c r="AA60" s="3">
@@ -8416,32 +8424,32 @@
       <c r="X61" s="2">
         <v>2600336924</v>
       </c>
-      <c r="Y61" s="2">
+      <c r="Y61" s="7">
         <v>2649294866.04</v>
       </c>
-      <c r="Z61" s="2">
+      <c r="Z61" s="7">
         <v>2759648000</v>
       </c>
       <c r="AA61" s="3">
-        <v>2822152959.5433946</v>
+        <v>2821153662.6053987</v>
       </c>
       <c r="AB61" s="3">
-        <v>2819104889.5085387</v>
+        <v>2819402350.5282969</v>
       </c>
       <c r="AC61" s="3">
-        <v>2786886980.6725488</v>
+        <v>2789485827.128808</v>
       </c>
       <c r="AD61" s="3">
-        <v>2788774609.6967082</v>
+        <v>2792486666.0616698</v>
       </c>
       <c r="AE61" s="3">
-        <v>2799900402.704772</v>
+        <v>2804419760.781003</v>
       </c>
       <c r="AF61" s="3">
-        <v>2804159200.2920818</v>
+        <v>2809720929.5632424</v>
       </c>
       <c r="AG61" s="3">
-        <v>2804151727.3642411</v>
+        <v>2810899087.2423797</v>
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
@@ -8517,10 +8525,10 @@
       <c r="X62" s="2">
         <v>277388928</v>
       </c>
-      <c r="Y62" s="2">
+      <c r="Y62" s="7">
         <v>213297322.37</v>
       </c>
-      <c r="Z62" s="2">
+      <c r="Z62" s="7">
         <v>281798000</v>
       </c>
       <c r="AA62" s="3">
@@ -8618,10 +8626,10 @@
       <c r="X63" s="2">
         <v>1263776206</v>
       </c>
-      <c r="Y63" s="2">
+      <c r="Y63" s="7">
         <v>1403088026.2</v>
       </c>
-      <c r="Z63" s="2">
+      <c r="Z63" s="7">
         <v>1482554000</v>
       </c>
       <c r="AA63" s="3">
@@ -8719,10 +8727,10 @@
       <c r="X64" s="2">
         <v>1591733178</v>
       </c>
-      <c r="Y64" s="2">
+      <c r="Y64" s="7">
         <v>648616292.55999994</v>
       </c>
-      <c r="Z64" s="2">
+      <c r="Z64" s="7">
         <v>689019000</v>
       </c>
       <c r="AA64" s="3">
@@ -8820,10 +8828,10 @@
       <c r="X65" s="2">
         <v>626589813</v>
       </c>
-      <c r="Y65" s="2">
+      <c r="Y65" s="7">
         <v>685442959.86000001</v>
       </c>
-      <c r="Z65" s="2">
+      <c r="Z65" s="7">
         <v>676611000</v>
       </c>
       <c r="AA65" s="3">
@@ -8921,10 +8929,10 @@
       <c r="X66" s="2">
         <v>193741092</v>
       </c>
-      <c r="Y66" s="2">
+      <c r="Y66" s="7">
         <v>233409396.02000001</v>
       </c>
-      <c r="Z66" s="2">
+      <c r="Z66" s="7">
         <v>248344000</v>
       </c>
       <c r="AA66" s="3">
@@ -9022,10 +9030,10 @@
       <c r="X67" s="2">
         <v>77784190</v>
       </c>
-      <c r="Y67" s="2">
+      <c r="Y67" s="7">
         <v>91407660.120000005</v>
       </c>
-      <c r="Z67" s="2">
+      <c r="Z67" s="7">
         <v>96487000</v>
       </c>
       <c r="AA67" s="3">
@@ -9123,10 +9131,10 @@
       <c r="X68" s="2">
         <v>166910899</v>
       </c>
-      <c r="Y68" s="2">
+      <c r="Y68" s="7">
         <v>116857535.31</v>
       </c>
-      <c r="Z68" s="2">
+      <c r="Z68" s="7">
         <v>152293000</v>
       </c>
       <c r="AA68" s="3">
@@ -9224,32 +9232,32 @@
       <c r="X69" s="2">
         <v>115587474</v>
       </c>
-      <c r="Y69" s="2">
+      <c r="Y69" s="7">
         <v>121668349.45999999</v>
       </c>
-      <c r="Z69" s="2">
+      <c r="Z69" s="7">
         <v>147115000</v>
       </c>
       <c r="AA69" s="3">
-        <v>149032445.48949575</v>
+        <v>147502091.8840459</v>
       </c>
       <c r="AB69" s="3">
-        <v>153035928.95747051</v>
+        <v>151190458.05393559</v>
       </c>
       <c r="AC69" s="3">
-        <v>158069913.84593937</v>
+        <v>156446264.28000012</v>
       </c>
       <c r="AD69" s="3">
-        <v>162154278.81832126</v>
+        <v>160099052.5588508</v>
       </c>
       <c r="AE69" s="3">
-        <v>166031171.23322475</v>
+        <v>163337141.01281294</v>
       </c>
       <c r="AF69" s="3">
-        <v>170239606.11622417</v>
+        <v>167020880.34252366</v>
       </c>
       <c r="AG69" s="3">
-        <v>174705888.51932231</v>
+        <v>171027655.8721444</v>
       </c>
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
@@ -9325,10 +9333,10 @@
       <c r="X70" s="2">
         <v>16163715855</v>
       </c>
-      <c r="Y70" s="2">
+      <c r="Y70" s="7">
         <v>17108644357.85</v>
       </c>
-      <c r="Z70" s="2">
+      <c r="Z70" s="7">
         <v>17619284000</v>
       </c>
       <c r="AA70" s="3">
@@ -9426,10 +9434,10 @@
       <c r="X71" s="2">
         <v>1048673173</v>
       </c>
-      <c r="Y71" s="2">
+      <c r="Y71" s="7">
         <v>1095578287.5699999</v>
       </c>
-      <c r="Z71" s="2">
+      <c r="Z71" s="7">
         <v>1084930000</v>
       </c>
       <c r="AA71" s="3">
@@ -9527,10 +9535,10 @@
       <c r="X72" s="2">
         <v>5381888596</v>
       </c>
-      <c r="Y72" s="2">
+      <c r="Y72" s="7">
         <v>5605948276.8100004</v>
       </c>
-      <c r="Z72" s="2">
+      <c r="Z72" s="7">
         <v>5510392000</v>
       </c>
       <c r="AA72" s="3">
@@ -9628,10 +9636,10 @@
       <c r="X73" s="2">
         <v>512919119</v>
       </c>
-      <c r="Y73" s="2">
+      <c r="Y73" s="7">
         <v>492623644.17000002</v>
       </c>
-      <c r="Z73" s="2">
+      <c r="Z73" s="7">
         <v>529198000</v>
       </c>
       <c r="AA73" s="3">
@@ -9729,10 +9737,10 @@
       <c r="X74" s="2">
         <v>450375923</v>
       </c>
-      <c r="Y74" s="2">
+      <c r="Y74" s="7">
         <v>446438294.44999999</v>
       </c>
-      <c r="Z74" s="2">
+      <c r="Z74" s="7">
         <v>484593000</v>
       </c>
       <c r="AA74" s="3">
@@ -9830,10 +9838,10 @@
       <c r="X75" s="2">
         <v>67722277</v>
       </c>
-      <c r="Y75" s="2">
+      <c r="Y75" s="7">
         <v>59631745.090000004</v>
       </c>
-      <c r="Z75" s="2">
+      <c r="Z75" s="7">
         <v>74761000</v>
       </c>
       <c r="AA75" s="3">
@@ -9931,10 +9939,10 @@
       <c r="X76" s="2">
         <v>697976869</v>
       </c>
-      <c r="Y76" s="2">
+      <c r="Y76" s="7">
         <v>712136349.98000002</v>
       </c>
-      <c r="Z76" s="2">
+      <c r="Z76" s="7">
         <v>763282000</v>
       </c>
       <c r="AA76" s="3">
@@ -10032,32 +10040,32 @@
       <c r="X77" s="2">
         <v>941399612</v>
       </c>
-      <c r="Y77" s="2">
+      <c r="Y77" s="7">
         <v>918261823.23000002</v>
       </c>
-      <c r="Z77" s="2">
+      <c r="Z77" s="7">
         <v>1055553000</v>
       </c>
       <c r="AA77" s="3">
-        <v>1095355303.0673075</v>
+        <v>1093671289.3655777</v>
       </c>
       <c r="AB77" s="3">
-        <v>1127195042.4174867</v>
+        <v>1125611400.9935498</v>
       </c>
       <c r="AC77" s="3">
-        <v>1155713398.8002028</v>
+        <v>1155093526.2421265</v>
       </c>
       <c r="AD77" s="3">
-        <v>1190047086.9329979</v>
+        <v>1189418353.0858438</v>
       </c>
       <c r="AE77" s="3">
-        <v>1226835837.0854733</v>
+        <v>1225909974.6628807</v>
       </c>
       <c r="AF77" s="3">
-        <v>1263659284.1106219</v>
+        <v>1262640280.1053357</v>
       </c>
       <c r="AG77" s="3">
-        <v>1300886957.4198132</v>
+        <v>1299911040.6369858</v>
       </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
@@ -10133,10 +10141,10 @@
       <c r="X78" s="2">
         <v>11879929503</v>
       </c>
-      <c r="Y78" s="2">
+      <c r="Y78" s="7">
         <v>12282988005.33</v>
       </c>
-      <c r="Z78" s="2">
+      <c r="Z78" s="7">
         <v>12339548000</v>
       </c>
       <c r="AA78" s="3">
@@ -10234,10 +10242,10 @@
       <c r="X79" s="2">
         <v>1094785649</v>
       </c>
-      <c r="Y79" s="2">
+      <c r="Y79" s="7">
         <v>1110457738.04</v>
       </c>
-      <c r="Z79" s="2">
+      <c r="Z79" s="7">
         <v>1090031000</v>
       </c>
       <c r="AA79" s="3">
@@ -10335,10 +10343,10 @@
       <c r="X80" s="2">
         <v>78636354</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Y80" s="7">
         <v>86745848.629999995</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="Z80" s="7">
         <v>106831000</v>
       </c>
       <c r="AA80" s="3">
@@ -10436,10 +10444,10 @@
       <c r="X81" s="2">
         <v>2213441341</v>
       </c>
-      <c r="Y81" s="2">
+      <c r="Y81" s="7">
         <v>2196200753.7800002</v>
       </c>
-      <c r="Z81" s="2">
+      <c r="Z81" s="7">
         <v>2003888000</v>
       </c>
       <c r="AA81" s="3">
@@ -10537,10 +10545,10 @@
       <c r="X82" s="2">
         <v>352911695</v>
       </c>
-      <c r="Y82" s="2">
+      <c r="Y82" s="7">
         <v>359929097.12</v>
       </c>
-      <c r="Z82" s="2">
+      <c r="Z82" s="7">
         <v>382121000</v>
       </c>
       <c r="AA82" s="3">
@@ -10638,10 +10646,10 @@
       <c r="X83" s="2">
         <v>751010524</v>
       </c>
-      <c r="Y83" s="2">
+      <c r="Y83" s="7">
         <v>641386376.23000002</v>
       </c>
-      <c r="Z83" s="2">
+      <c r="Z83" s="7">
         <v>674813000</v>
       </c>
       <c r="AA83" s="3">
@@ -10739,32 +10747,32 @@
       <c r="X84" s="2">
         <v>195611840</v>
       </c>
-      <c r="Y84" s="2">
+      <c r="Y84" s="7">
         <v>193581858.75999999</v>
       </c>
-      <c r="Z84" s="2">
+      <c r="Z84" s="7">
         <v>184448000</v>
       </c>
       <c r="AA84" s="3">
-        <v>193774402.41493395</v>
+        <v>194395817.20130509</v>
       </c>
       <c r="AB84" s="3">
-        <v>198539974.45611683</v>
+        <v>199661269.25047866</v>
       </c>
       <c r="AC84" s="3">
-        <v>201174171.37867111</v>
+        <v>202731773.70571566</v>
       </c>
       <c r="AD84" s="3">
-        <v>206508652.33781198</v>
+        <v>208626090.10196784</v>
       </c>
       <c r="AE84" s="3">
-        <v>212733166.495998</v>
+        <v>215473551.53721267</v>
       </c>
       <c r="AF84" s="3">
-        <v>218570592.23514682</v>
+        <v>221944009.69887528</v>
       </c>
       <c r="AG84" s="3">
-        <v>224203708.77619323</v>
+        <v>228226167.6605663</v>
       </c>
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
@@ -10840,32 +10848,32 @@
       <c r="X85" s="2">
         <v>207394605</v>
       </c>
-      <c r="Y85" s="2">
+      <c r="Y85" s="7">
         <v>180898006.46000001</v>
       </c>
-      <c r="Z85" s="2">
+      <c r="Z85" s="7">
         <v>184032000</v>
       </c>
       <c r="AA85" s="3">
-        <v>190245604.65128061</v>
+        <v>190585184.44620037</v>
       </c>
       <c r="AB85" s="3">
-        <v>197655461.65115717</v>
+        <v>197942966.2196207</v>
       </c>
       <c r="AC85" s="3">
-        <v>205800868.28690323</v>
+        <v>205843538.6547218</v>
       </c>
       <c r="AD85" s="3">
-        <v>213737557.07306552</v>
+        <v>213744696.05735198</v>
       </c>
       <c r="AE85" s="3">
-        <v>221825632.32406744</v>
+        <v>221859710.7064015</v>
       </c>
       <c r="AF85" s="3">
-        <v>230339417.91048735</v>
+        <v>230351993.34573373</v>
       </c>
       <c r="AG85" s="3">
-        <v>239256658.26220524</v>
+        <v>239213675.32513747</v>
       </c>
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
@@ -10941,10 +10949,10 @@
       <c r="X86" s="2">
         <v>71532231</v>
       </c>
-      <c r="Y86" s="2">
+      <c r="Y86" s="7">
         <v>74344663.170000002</v>
       </c>
-      <c r="Z86" s="2">
+      <c r="Z86" s="7">
         <v>75981000</v>
       </c>
       <c r="AA86" s="3">
@@ -11042,10 +11050,10 @@
       <c r="X87" s="2">
         <v>208381322</v>
       </c>
-      <c r="Y87" s="2">
+      <c r="Y87" s="7">
         <v>198280920.91</v>
       </c>
-      <c r="Z87" s="2">
+      <c r="Z87" s="7">
         <v>241247000</v>
       </c>
       <c r="AA87" s="3">
@@ -11143,10 +11151,10 @@
       <c r="X88" s="2">
         <v>216167649</v>
       </c>
-      <c r="Y88" s="2">
+      <c r="Y88" s="7">
         <v>261959841.47</v>
       </c>
-      <c r="Z88" s="2">
+      <c r="Z88" s="7">
         <v>253179000</v>
       </c>
       <c r="AA88" s="3">
@@ -11244,10 +11252,10 @@
       <c r="X89" s="2">
         <v>895092390</v>
       </c>
-      <c r="Y89" s="2">
+      <c r="Y89" s="7">
         <v>879557284.04999995</v>
       </c>
-      <c r="Z89" s="2">
+      <c r="Z89" s="7">
         <v>845387000</v>
       </c>
       <c r="AA89" s="3">
@@ -11345,10 +11353,10 @@
       <c r="X90" s="2">
         <v>75866230</v>
       </c>
-      <c r="Y90" s="2">
+      <c r="Y90" s="7">
         <v>87304608.650000006</v>
       </c>
-      <c r="Z90" s="2">
+      <c r="Z90" s="7">
         <v>95653000</v>
       </c>
       <c r="AA90" s="3">
@@ -11446,10 +11454,10 @@
       <c r="X91" s="2">
         <v>27807404637</v>
       </c>
-      <c r="Y91" s="2">
+      <c r="Y91" s="7">
         <v>29091046866.290001</v>
       </c>
-      <c r="Z91" s="2">
+      <c r="Z91" s="7">
         <v>31190132000</v>
       </c>
       <c r="AA91" s="3">
@@ -11547,10 +11555,10 @@
       <c r="X92" s="2">
         <v>92813913</v>
       </c>
-      <c r="Y92" s="2">
+      <c r="Y92" s="7">
         <v>95447166.329999998</v>
       </c>
-      <c r="Z92" s="2">
+      <c r="Z92" s="7">
         <v>104803000</v>
       </c>
       <c r="AA92" s="3">
@@ -11648,10 +11656,10 @@
       <c r="X93" s="2">
         <v>1445313172</v>
       </c>
-      <c r="Y93" s="2">
+      <c r="Y93" s="7">
         <v>1466670533.27</v>
       </c>
-      <c r="Z93" s="2">
+      <c r="Z93" s="7">
         <v>1525924000</v>
       </c>
       <c r="AA93" s="3">
@@ -11749,10 +11757,10 @@
       <c r="X94" s="2">
         <v>1503278050</v>
       </c>
-      <c r="Y94" s="2">
+      <c r="Y94" s="7">
         <v>1519139194.1199999</v>
       </c>
-      <c r="Z94" s="2">
+      <c r="Z94" s="7">
         <v>1596213000</v>
       </c>
       <c r="AA94" s="3">
@@ -11850,10 +11858,10 @@
       <c r="X95" s="2">
         <v>120504532</v>
       </c>
-      <c r="Y95" s="2">
+      <c r="Y95" s="7">
         <v>106253146.73999999</v>
       </c>
-      <c r="Z95" s="2">
+      <c r="Z95" s="7">
         <v>114310000</v>
       </c>
       <c r="AA95" s="3">
@@ -11951,10 +11959,10 @@
       <c r="X96" s="2">
         <v>117984628</v>
       </c>
-      <c r="Y96" s="2">
+      <c r="Y96" s="7">
         <v>134962455.34</v>
       </c>
-      <c r="Z96" s="2">
+      <c r="Z96" s="7">
         <v>159894000</v>
       </c>
       <c r="AA96" s="3">
@@ -12052,10 +12060,10 @@
       <c r="X97" s="2">
         <v>912789553</v>
       </c>
-      <c r="Y97" s="2">
+      <c r="Y97" s="7">
         <v>945861281.05999994</v>
       </c>
-      <c r="Z97" s="2">
+      <c r="Z97" s="7">
         <v>1005308000</v>
       </c>
       <c r="AA97" s="3">
@@ -12153,32 +12161,32 @@
       <c r="X98" s="2">
         <v>2399800943</v>
       </c>
-      <c r="Y98" s="2">
+      <c r="Y98" s="7">
         <v>1936667683.73</v>
       </c>
-      <c r="Z98" s="2">
+      <c r="Z98" s="7">
         <v>1982039000</v>
       </c>
       <c r="AA98" s="3">
-        <v>2224279005.4609976</v>
+        <v>2226904968.4641118</v>
       </c>
       <c r="AB98" s="3">
-        <v>2367414245.9930053</v>
+        <v>2372806318.3437757</v>
       </c>
       <c r="AC98" s="3">
-        <v>2460018387.6636505</v>
+        <v>2468224513.758791</v>
       </c>
       <c r="AD98" s="3">
-        <v>2628866106.8445864</v>
+        <v>2640543035.275013</v>
       </c>
       <c r="AE98" s="3">
-        <v>2830536145.5307074</v>
+        <v>2846277871.0189157</v>
       </c>
       <c r="AF98" s="3">
-        <v>3030638789.2953196</v>
+        <v>3050862324.0001001</v>
       </c>
       <c r="AG98" s="3">
-        <v>3233626648.3029642</v>
+        <v>3258784764.0075417</v>
       </c>
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
@@ -12254,32 +12262,32 @@
       <c r="X99" s="2">
         <v>4906888429</v>
       </c>
-      <c r="Y99" s="2">
+      <c r="Y99" s="7">
         <v>5438473657.96</v>
       </c>
-      <c r="Z99" s="2">
+      <c r="Z99" s="7">
         <v>5058949000</v>
       </c>
       <c r="AA99" s="3">
-        <v>5457852854.3468199</v>
+        <v>5476216039.9731121</v>
       </c>
       <c r="AB99" s="3">
-        <v>5609659752.1991215</v>
+        <v>5654352269.3638363</v>
       </c>
       <c r="AC99" s="3">
-        <v>5640835892.3643799</v>
+        <v>5715110226.1551533</v>
       </c>
       <c r="AD99" s="3">
-        <v>5819052960.8636341</v>
+        <v>5922159647.3197594</v>
       </c>
       <c r="AE99" s="3">
-        <v>6044353611.4768581</v>
+        <v>6178000883.2389812</v>
       </c>
       <c r="AF99" s="3">
-        <v>6246287861.8131514</v>
+        <v>6412792734.5641117</v>
       </c>
       <c r="AG99" s="3">
-        <v>6434498478.1300507</v>
+        <v>6635938775.9821959</v>
       </c>
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
@@ -12355,10 +12363,10 @@
       <c r="X100" s="2">
         <v>530853519</v>
       </c>
-      <c r="Y100" s="2">
+      <c r="Y100" s="7">
         <v>608003204.46000004</v>
       </c>
-      <c r="Z100" s="2">
+      <c r="Z100" s="7">
         <v>661697000</v>
       </c>
       <c r="AA100" s="3">
@@ -12456,10 +12464,10 @@
       <c r="X101" s="2">
         <v>388509030</v>
       </c>
-      <c r="Y101" s="2">
+      <c r="Y101" s="7">
         <v>389123760</v>
       </c>
-      <c r="Z101" s="2">
+      <c r="Z101" s="7">
         <v>406387000</v>
       </c>
       <c r="AA101" s="3">
@@ -12557,10 +12565,10 @@
       <c r="X102" s="2">
         <v>457128322</v>
       </c>
-      <c r="Y102" s="2">
+      <c r="Y102" s="7">
         <v>427781188.05000001</v>
       </c>
-      <c r="Z102" s="2">
+      <c r="Z102" s="7">
         <v>456981000</v>
       </c>
       <c r="AA102" s="3">
@@ -12658,32 +12666,32 @@
       <c r="X103" s="2">
         <v>1490610073</v>
       </c>
-      <c r="Y103" s="2">
+      <c r="Y103" s="7">
         <v>1456059571.0599999</v>
       </c>
-      <c r="Z103" s="2">
+      <c r="Z103" s="7">
         <v>1492565000</v>
       </c>
       <c r="AA103" s="3">
-        <v>1649037429.2008119</v>
+        <v>1644210063.9196258</v>
       </c>
       <c r="AB103" s="3">
-        <v>1713962875.3994391</v>
+        <v>1718089522.7721756</v>
       </c>
       <c r="AC103" s="3">
-        <v>1732514393.6709776</v>
+        <v>1752830784.5336354</v>
       </c>
       <c r="AD103" s="3">
-        <v>1809125809.994236</v>
+        <v>1838946965.488174</v>
       </c>
       <c r="AE103" s="3">
-        <v>1905655401.8306451</v>
+        <v>1943839276.9999585</v>
       </c>
       <c r="AF103" s="3">
-        <v>1994358654.1421711</v>
+        <v>2043256205.9573061</v>
       </c>
       <c r="AG103" s="3">
-        <v>2078807581.6542108</v>
+        <v>2140323003.9218795</v>
       </c>
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
@@ -12759,10 +12767,10 @@
       <c r="X104" s="2">
         <v>536600317</v>
       </c>
-      <c r="Y104" s="2">
+      <c r="Y104" s="7">
         <v>557701655.98000002</v>
       </c>
-      <c r="Z104" s="2">
+      <c r="Z104" s="7">
         <v>615278000</v>
       </c>
       <c r="AA104" s="3">
@@ -12860,32 +12868,32 @@
       <c r="X105" s="2">
         <v>2967715347</v>
       </c>
-      <c r="Y105" s="2">
+      <c r="Y105" s="7">
         <v>3186447300.8299999</v>
       </c>
-      <c r="Z105" s="2">
+      <c r="Z105" s="7">
         <v>3136750000</v>
       </c>
       <c r="AA105" s="3">
-        <v>3343161618.401329</v>
+        <v>3346774249.2554955</v>
       </c>
       <c r="AB105" s="3">
-        <v>3463040394.4034767</v>
+        <v>3468835195.8420763</v>
       </c>
       <c r="AC105" s="3">
-        <v>3541992394.3340697</v>
+        <v>3549232347.4586806</v>
       </c>
       <c r="AD105" s="3">
-        <v>3676856171.4744864</v>
+        <v>3686690107.9101748</v>
       </c>
       <c r="AE105" s="3">
-        <v>3832223837.9424896</v>
+        <v>3845158466.3684955</v>
       </c>
       <c r="AF105" s="3">
-        <v>3982218807.3708439</v>
+        <v>3998244923.9154124</v>
       </c>
       <c r="AG105" s="3">
-        <v>4130427225.0028987</v>
+        <v>4149599715.8761539</v>
       </c>
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
@@ -12961,10 +12969,10 @@
       <c r="X106" s="2">
         <v>239084023</v>
       </c>
-      <c r="Y106" s="2">
+      <c r="Y106" s="7">
         <v>245450126.5</v>
       </c>
-      <c r="Z106" s="2">
+      <c r="Z106" s="7">
         <v>262918000</v>
       </c>
       <c r="AA106" s="3">
@@ -13062,10 +13070,10 @@
       <c r="X107" s="2">
         <v>418999280</v>
       </c>
-      <c r="Y107" s="2">
+      <c r="Y107" s="7">
         <v>520641624.20999998</v>
       </c>
-      <c r="Z107" s="2">
+      <c r="Z107" s="7">
         <v>617585000</v>
       </c>
       <c r="AA107" s="3">
@@ -13163,10 +13171,10 @@
       <c r="X108" s="2">
         <v>736523731</v>
       </c>
-      <c r="Y108" s="2">
+      <c r="Y108" s="7">
         <v>728288896.78999996</v>
       </c>
-      <c r="Z108" s="2">
+      <c r="Z108" s="7">
         <v>723522000</v>
       </c>
       <c r="AA108" s="3">
@@ -13264,10 +13272,10 @@
       <c r="X109" s="2">
         <v>89238836</v>
       </c>
-      <c r="Y109" s="2">
+      <c r="Y109" s="7">
         <v>81569101.450000003</v>
       </c>
-      <c r="Z109" s="2">
+      <c r="Z109" s="7">
         <v>90693000</v>
       </c>
       <c r="AA109" s="3">
@@ -13365,10 +13373,10 @@
       <c r="X110" s="2">
         <v>171634392</v>
       </c>
-      <c r="Y110" s="2">
+      <c r="Y110" s="7">
         <v>169832366.99000001</v>
       </c>
-      <c r="Z110" s="2">
+      <c r="Z110" s="7">
         <v>174344000</v>
       </c>
       <c r="AA110" s="3">
@@ -13466,32 +13474,32 @@
       <c r="X111" s="2">
         <v>707247992</v>
       </c>
-      <c r="Y111" s="2">
+      <c r="Y111" s="7">
         <v>745145919.46000004</v>
       </c>
-      <c r="Z111" s="2">
+      <c r="Z111" s="7">
         <v>774395000</v>
       </c>
       <c r="AA111" s="3">
-        <v>801159917.03513646</v>
+        <v>798346848.17841291</v>
       </c>
       <c r="AB111" s="3">
-        <v>808789405.98231816</v>
+        <v>807530009.90173197</v>
       </c>
       <c r="AC111" s="3">
-        <v>807659980.96055639</v>
+        <v>809977396.77915668</v>
       </c>
       <c r="AD111" s="3">
-        <v>816849067.71873868</v>
+        <v>820459681.4359144</v>
       </c>
       <c r="AE111" s="3">
-        <v>828997561.26158273</v>
+        <v>833302387.82229447</v>
       </c>
       <c r="AF111" s="3">
-        <v>839167465.58900785</v>
+        <v>844662130.67571199</v>
       </c>
       <c r="AG111" s="3">
-        <v>848112907.73491299</v>
+        <v>855123066.7370342</v>
       </c>
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.25">
@@ -13567,10 +13575,10 @@
       <c r="X112" s="2">
         <v>4156614401</v>
       </c>
-      <c r="Y112" s="2">
+      <c r="Y112" s="7">
         <v>4746064823.2700005</v>
       </c>
-      <c r="Z112" s="2">
+      <c r="Z112" s="7">
         <v>4878274000</v>
       </c>
       <c r="AA112" s="3">
@@ -13668,32 +13676,32 @@
       <c r="X113" s="2">
         <v>1434464011</v>
       </c>
-      <c r="Y113" s="2">
+      <c r="Y113" s="7">
         <v>1355977983.4400001</v>
       </c>
-      <c r="Z113" s="2">
+      <c r="Z113" s="7">
         <v>1190605000</v>
       </c>
       <c r="AA113" s="3">
-        <v>1278783695.0297763</v>
+        <v>1292776246.4549623</v>
       </c>
       <c r="AB113" s="3">
-        <v>1350682447.4079912</v>
+        <v>1368426721.5483453</v>
       </c>
       <c r="AC113" s="3">
-        <v>1416116776.4584651</v>
+        <v>1432214431.2211828</v>
       </c>
       <c r="AD113" s="3">
-        <v>1497607725.793855</v>
+        <v>1518919815.8384778</v>
       </c>
       <c r="AE113" s="3">
-        <v>1587516814.6524444</v>
+        <v>1616661456.3960252</v>
       </c>
       <c r="AF113" s="3">
-        <v>1679877901.9813616</v>
+        <v>1716102214.0425246</v>
       </c>
       <c r="AG113" s="3">
-        <v>1775688404.4252901</v>
+        <v>1818651644.4719141</v>
       </c>
     </row>
     <row r="114" spans="1:33" x14ac:dyDescent="0.25">
@@ -13769,10 +13777,10 @@
       <c r="X114" s="2">
         <v>298426291</v>
       </c>
-      <c r="Y114" s="2">
+      <c r="Y114" s="7">
         <v>306235546.68000001</v>
       </c>
-      <c r="Z114" s="2">
+      <c r="Z114" s="7">
         <v>320780000</v>
       </c>
       <c r="AA114" s="3">
@@ -13870,10 +13878,10 @@
       <c r="X115" s="2">
         <v>2954222352</v>
       </c>
-      <c r="Y115" s="2">
+      <c r="Y115" s="7">
         <v>3102338580.3299999</v>
       </c>
-      <c r="Z115" s="2">
+      <c r="Z115" s="7">
         <v>3250688000</v>
       </c>
       <c r="AA115" s="3">
@@ -13971,32 +13979,32 @@
       <c r="X116" s="2">
         <v>307684431</v>
       </c>
-      <c r="Y116" s="2">
+      <c r="Y116" s="7">
         <v>319262324.24000001</v>
       </c>
-      <c r="Z116" s="2">
+      <c r="Z116" s="7">
         <v>319441000</v>
       </c>
       <c r="AA116" s="3">
-        <v>329046166.43422544</v>
+        <v>329625004.72186655</v>
       </c>
       <c r="AB116" s="3">
-        <v>338368837.62910903</v>
+        <v>339051225.30309224</v>
       </c>
       <c r="AC116" s="3">
-        <v>347699438.85542935</v>
+        <v>348261453.13735086</v>
       </c>
       <c r="AD116" s="3">
-        <v>357595310.93497866</v>
+        <v>358305313.77238965</v>
       </c>
       <c r="AE116" s="3">
-        <v>367859491.0865649</v>
+        <v>368803073.88320309</v>
       </c>
       <c r="AF116" s="3">
-        <v>378351847.82214266</v>
+        <v>379482417.0626905</v>
       </c>
       <c r="AG116" s="3">
-        <v>389101293.53942025</v>
+        <v>390390980.03460342</v>
       </c>
     </row>
     <row r="117" spans="1:33" x14ac:dyDescent="0.25">
@@ -14072,32 +14080,32 @@
       <c r="X117" s="2">
         <v>4338712001</v>
       </c>
-      <c r="Y117" s="2">
+      <c r="Y117" s="7">
         <v>4430148485.4700003</v>
       </c>
-      <c r="Z117" s="2">
+      <c r="Z117" s="7">
         <v>4484718000</v>
       </c>
       <c r="AA117" s="3">
-        <v>4753751328.524209</v>
+        <v>4747257320.9739571</v>
       </c>
       <c r="AB117" s="3">
-        <v>4870387015.1312256</v>
+        <v>4878120862.0737247</v>
       </c>
       <c r="AC117" s="3">
-        <v>4914583269.1649361</v>
+        <v>4946698630.0590487</v>
       </c>
       <c r="AD117" s="3">
-        <v>5048068855.5407295</v>
+        <v>5094407397.522295</v>
       </c>
       <c r="AE117" s="3">
-        <v>5210160709.7299843</v>
+        <v>5268552061.9576435</v>
       </c>
       <c r="AF117" s="3">
-        <v>5358242309.83109</v>
+        <v>5431673823.822794</v>
       </c>
       <c r="AG117" s="3">
-        <v>5498334508.3089199</v>
+        <v>5589042814.6992102</v>
       </c>
     </row>
     <row r="118" spans="1:33" x14ac:dyDescent="0.25">
@@ -14173,10 +14181,10 @@
       <c r="X118" s="2">
         <v>268844859</v>
       </c>
-      <c r="Y118" s="2">
+      <c r="Y118" s="7">
         <v>302545539.37</v>
       </c>
-      <c r="Z118" s="2">
+      <c r="Z118" s="7">
         <v>381384000</v>
       </c>
       <c r="AA118" s="3">
@@ -14274,10 +14282,10 @@
       <c r="X119" s="2">
         <v>126449618</v>
       </c>
-      <c r="Y119" s="2">
+      <c r="Y119" s="7">
         <v>129016591.44</v>
       </c>
-      <c r="Z119" s="2">
+      <c r="Z119" s="7">
         <v>134995000</v>
       </c>
       <c r="AA119" s="3">
@@ -14375,10 +14383,10 @@
       <c r="X120" s="2">
         <v>450054886</v>
       </c>
-      <c r="Y120" s="2">
+      <c r="Y120" s="7">
         <v>448446543.68000001</v>
       </c>
-      <c r="Z120" s="2">
+      <c r="Z120" s="7">
         <v>486274000</v>
       </c>
       <c r="AA120" s="3">
@@ -14476,10 +14484,10 @@
       <c r="X121" s="2">
         <v>379157648</v>
       </c>
-      <c r="Y121" s="2">
+      <c r="Y121" s="7">
         <v>414300828.82999998</v>
       </c>
-      <c r="Z121" s="2">
+      <c r="Z121" s="7">
         <v>435900000</v>
       </c>
       <c r="AA121" s="3">
@@ -14577,10 +14585,10 @@
       <c r="X122" s="2">
         <v>549693196</v>
       </c>
-      <c r="Y122" s="2">
+      <c r="Y122" s="7">
         <v>568287419.21000004</v>
       </c>
-      <c r="Z122" s="2">
+      <c r="Z122" s="7">
         <v>564808000</v>
       </c>
       <c r="AA122" s="3">
@@ -14678,10 +14686,10 @@
       <c r="X123" s="2">
         <v>157928945</v>
       </c>
-      <c r="Y123" s="2">
+      <c r="Y123" s="7">
         <v>215660548.53999999</v>
       </c>
-      <c r="Z123" s="2">
+      <c r="Z123" s="7">
         <v>258923000</v>
       </c>
       <c r="AA123" s="3">
@@ -14779,10 +14787,10 @@
       <c r="X124" s="2">
         <v>333654198</v>
       </c>
-      <c r="Y124" s="2">
+      <c r="Y124" s="7">
         <v>341487825.47000003</v>
       </c>
-      <c r="Z124" s="2">
+      <c r="Z124" s="7">
         <v>339803000</v>
       </c>
       <c r="AA124" s="3">
@@ -14880,10 +14888,10 @@
       <c r="X125" s="2">
         <v>66826442</v>
       </c>
-      <c r="Y125" s="2">
+      <c r="Y125" s="7">
         <v>73187701.260000005</v>
       </c>
-      <c r="Z125" s="2">
+      <c r="Z125" s="7">
         <v>78560000</v>
       </c>
       <c r="AA125" s="3">
@@ -14981,32 +14989,32 @@
       <c r="X126" s="2">
         <v>541722745</v>
       </c>
-      <c r="Y126" s="2">
+      <c r="Y126" s="7">
         <v>583312585.52999997</v>
       </c>
-      <c r="Z126" s="2">
+      <c r="Z126" s="7">
         <v>636426000</v>
       </c>
       <c r="AA126" s="3">
-        <v>656373646.28172791</v>
+        <v>655802052.68993449</v>
       </c>
       <c r="AB126" s="3">
-        <v>669644546.11327577</v>
+        <v>669192584.544873</v>
       </c>
       <c r="AC126" s="3">
-        <v>679935035.01018286</v>
+        <v>679930476.66863441</v>
       </c>
       <c r="AD126" s="3">
-        <v>694242493.66655111</v>
+        <v>694318557.00937259</v>
       </c>
       <c r="AE126" s="3">
-        <v>709929020.15410542</v>
+        <v>709982801.18955123</v>
       </c>
       <c r="AF126" s="3">
-        <v>725148435.33352065</v>
+        <v>725259932.24233961</v>
       </c>
       <c r="AG126" s="3">
-        <v>740176124.45516551</v>
+        <v>740398854.01073849</v>
       </c>
     </row>
     <row r="127" spans="1:33" x14ac:dyDescent="0.25">
@@ -15082,10 +15090,10 @@
       <c r="X127" s="2">
         <v>477698294</v>
       </c>
-      <c r="Y127" s="2">
+      <c r="Y127" s="7">
         <v>534567895.82999998</v>
       </c>
-      <c r="Z127" s="2">
+      <c r="Z127" s="7">
         <v>550222000</v>
       </c>
       <c r="AA127" s="3">
@@ -15183,32 +15191,32 @@
       <c r="X128" s="2">
         <v>1236552979</v>
       </c>
-      <c r="Y128" s="2">
+      <c r="Y128" s="7">
         <v>1285784578.49</v>
       </c>
-      <c r="Z128" s="2">
+      <c r="Z128" s="7">
         <v>1404662000</v>
       </c>
       <c r="AA128" s="3">
-        <v>1464272399.9596958</v>
+        <v>1463223974.831039</v>
       </c>
       <c r="AB128" s="3">
-        <v>1510381849.56585</v>
+        <v>1509592681.4628761</v>
       </c>
       <c r="AC128" s="3">
-        <v>1550732249.7095726</v>
+        <v>1550846395.7087007</v>
       </c>
       <c r="AD128" s="3">
-        <v>1600821593.819783</v>
+        <v>1601140534.1908243</v>
       </c>
       <c r="AE128" s="3">
-        <v>1654975053.3770182</v>
+        <v>1655300964.7102027</v>
       </c>
       <c r="AF128" s="3">
-        <v>1709075703.4236445</v>
+        <v>1709571236.029289</v>
       </c>
       <c r="AG128" s="3">
-        <v>1763743442.2386782</v>
+        <v>1764522865.6568453</v>
       </c>
     </row>
     <row r="129" spans="1:33" x14ac:dyDescent="0.25">
@@ -15284,32 +15292,32 @@
       <c r="X129" s="2">
         <v>56367018966</v>
       </c>
-      <c r="Y129" s="2">
+      <c r="Y129" s="7">
         <v>55675172013.510002</v>
       </c>
-      <c r="Z129" s="2">
-        <v>60107728964.780403</v>
+      <c r="Z129" s="7">
+        <v>48195909000</v>
       </c>
       <c r="AA129" s="3">
-        <v>67449101788.24836</v>
+        <v>54209958091.155319</v>
       </c>
       <c r="AB129" s="3">
-        <v>72527054230.200287</v>
+        <v>57988495286.420036</v>
       </c>
       <c r="AC129" s="3">
-        <v>76505464244.221466</v>
+        <v>60637478687.494812</v>
       </c>
       <c r="AD129" s="3">
-        <v>82530683615.267197</v>
+        <v>65111380940.580963</v>
       </c>
       <c r="AE129" s="3">
-        <v>89570127237.624237</v>
+        <v>70415963921.048065</v>
       </c>
       <c r="AF129" s="3">
-        <v>96773468515.309616</v>
+        <v>75749241383.311478</v>
       </c>
       <c r="AG129" s="3">
-        <v>104264979230.69899</v>
+        <v>81218544183.56897</v>
       </c>
     </row>
     <row r="130" spans="1:33" x14ac:dyDescent="0.25">
@@ -15385,32 +15393,32 @@
       <c r="X130" s="2">
         <v>3410385203</v>
       </c>
-      <c r="Y130" s="2">
+      <c r="Y130" s="7">
         <v>3522214957.6100001</v>
       </c>
-      <c r="Z130" s="2">
+      <c r="Z130" s="7">
         <v>3799730000</v>
       </c>
       <c r="AA130" s="3">
-        <v>4053642500.6899595</v>
+        <v>4044694399.9207244</v>
       </c>
       <c r="AB130" s="3">
-        <v>4272251986.3549037</v>
+        <v>4266824200.1640134</v>
       </c>
       <c r="AC130" s="3">
-        <v>4478626768.3128424</v>
+        <v>4483382905.3787804</v>
       </c>
       <c r="AD130" s="3">
-        <v>4724432189.0962305</v>
+        <v>4732775884.2113237</v>
       </c>
       <c r="AE130" s="3">
-        <v>4992231587.3827648</v>
+        <v>5002350372.0734282</v>
       </c>
       <c r="AF130" s="3">
-        <v>5268514592.4356003</v>
+        <v>5282310076.966876</v>
       </c>
       <c r="AG130" s="3">
-        <v>5555725550.9906254</v>
+        <v>5574698655.3290043</v>
       </c>
     </row>
     <row r="131" spans="1:33" x14ac:dyDescent="0.25">
@@ -15486,10 +15494,10 @@
       <c r="X131" s="2">
         <v>1256804275</v>
       </c>
-      <c r="Y131" s="2">
+      <c r="Y131" s="7">
         <v>1347031249.5899999</v>
       </c>
-      <c r="Z131" s="2">
+      <c r="Z131" s="7">
         <v>1369949000</v>
       </c>
       <c r="AA131" s="3">
@@ -15587,32 +15595,32 @@
       <c r="X132" s="2">
         <v>1993444854</v>
       </c>
-      <c r="Y132" s="2">
+      <c r="Y132" s="7">
         <v>2165750524.27</v>
       </c>
-      <c r="Z132" s="2">
-        <v>2361126094.896348</v>
+      <c r="Z132" s="7">
+        <v>1990651000</v>
       </c>
       <c r="AA132" s="3">
-        <v>2563633936.4038239</v>
+        <v>2150961477.6631026</v>
       </c>
       <c r="AB132" s="3">
-        <v>2785057322.4972181</v>
+        <v>2319364936.2771783</v>
       </c>
       <c r="AC132" s="3">
-        <v>3026338133.2442832</v>
+        <v>2498687894.3300471</v>
       </c>
       <c r="AD132" s="3">
-        <v>3287590457.6934924</v>
+        <v>2694730028.3966289</v>
       </c>
       <c r="AE132" s="3">
-        <v>3571118808.7830973</v>
+        <v>2906995583.7419553</v>
       </c>
       <c r="AF132" s="3">
-        <v>3879323369.2670712</v>
+        <v>3135304212.2739196</v>
       </c>
       <c r="AG132" s="3">
-        <v>4214277762.2844381</v>
+        <v>3381092802.6207495</v>
       </c>
     </row>
     <row r="133" spans="1:33" x14ac:dyDescent="0.25">
@@ -15688,32 +15696,32 @@
       <c r="X133" s="2">
         <v>1652062163</v>
       </c>
-      <c r="Y133" s="2">
+      <c r="Y133" s="7">
         <v>1534236670.55</v>
       </c>
-      <c r="Z133" s="2">
+      <c r="Z133" s="7">
         <v>1565743000</v>
       </c>
       <c r="AA133" s="3">
-        <v>1648464104.0598986</v>
+        <v>1646914537.2149444</v>
       </c>
       <c r="AB133" s="3">
-        <v>1695720956.5456338</v>
+        <v>1697528634.8507154</v>
       </c>
       <c r="AC133" s="3">
-        <v>1726462918.2667644</v>
+        <v>1734071248.7542944</v>
       </c>
       <c r="AD133" s="3">
-        <v>1779045440.9410555</v>
+        <v>1790074835.1766846</v>
       </c>
       <c r="AE133" s="3">
-        <v>1839229968.0463362</v>
+        <v>1853161474.0752676</v>
       </c>
       <c r="AF133" s="3">
-        <v>1896827269.2252352</v>
+        <v>1914402119.8402054</v>
       </c>
       <c r="AG133" s="3">
-        <v>1953285075.8607259</v>
+        <v>1975071637.7212069</v>
       </c>
     </row>
     <row r="134" spans="1:33" x14ac:dyDescent="0.25">
@@ -15789,10 +15797,10 @@
       <c r="X134" s="2">
         <v>214049041</v>
       </c>
-      <c r="Y134" s="2">
+      <c r="Y134" s="7">
         <v>231298159.65000001</v>
       </c>
-      <c r="Z134" s="2">
+      <c r="Z134" s="7">
         <v>236970000</v>
       </c>
       <c r="AA134" s="3">
@@ -15890,10 +15898,10 @@
       <c r="X135" s="2">
         <v>625296223</v>
       </c>
-      <c r="Y135" s="2">
+      <c r="Y135" s="7">
         <v>656057661.20000005</v>
       </c>
-      <c r="Z135" s="2">
+      <c r="Z135" s="7">
         <v>733562000</v>
       </c>
       <c r="AA135" s="3">
@@ -15991,10 +15999,10 @@
       <c r="X136" s="2">
         <v>1005635334</v>
       </c>
-      <c r="Y136" s="2">
+      <c r="Y136" s="7">
         <v>893194315.19000006</v>
       </c>
-      <c r="Z136" s="2">
+      <c r="Z136" s="7">
         <v>887386000</v>
       </c>
       <c r="AA136" s="3">
@@ -16092,32 +16100,32 @@
       <c r="X137" s="2">
         <v>14226587024</v>
       </c>
-      <c r="Y137" s="2">
+      <c r="Y137" s="7">
         <v>15095350955.370001</v>
       </c>
-      <c r="Z137" s="2">
+      <c r="Z137" s="7">
         <v>15509263000</v>
       </c>
       <c r="AA137" s="3">
-        <v>16284289787.436186</v>
+        <v>16287783446.74613</v>
       </c>
       <c r="AB137" s="3">
-        <v>16498739913.132202</v>
+        <v>16514149924.729246</v>
       </c>
       <c r="AC137" s="3">
-        <v>16451218462.106358</v>
+        <v>16482245655.799486</v>
       </c>
       <c r="AD137" s="3">
-        <v>16712705414.188843</v>
+        <v>16755623214.803576</v>
       </c>
       <c r="AE137" s="3">
-        <v>17064199992.836325</v>
+        <v>17118429289.187208</v>
       </c>
       <c r="AF137" s="3">
-        <v>17357759476.710938</v>
+        <v>17424452575.86224</v>
       </c>
       <c r="AG137" s="3">
-        <v>17615349983.255024</v>
+        <v>17695333202.046444</v>
       </c>
     </row>
     <row r="138" spans="1:33" x14ac:dyDescent="0.25">
@@ -16193,10 +16201,10 @@
       <c r="X138" s="2">
         <v>79457831</v>
       </c>
-      <c r="Y138" s="2">
+      <c r="Y138" s="7">
         <v>78610960.209999993</v>
       </c>
-      <c r="Z138" s="2">
+      <c r="Z138" s="7">
         <v>82849000</v>
       </c>
       <c r="AA138" s="3">
@@ -16294,10 +16302,10 @@
       <c r="X139" s="2">
         <v>2810529980</v>
       </c>
-      <c r="Y139" s="2">
+      <c r="Y139" s="7">
         <v>2835581072</v>
       </c>
-      <c r="Z139" s="2">
+      <c r="Z139" s="7">
         <v>2754514000</v>
       </c>
       <c r="AA139" s="3">
@@ -16395,32 +16403,32 @@
       <c r="X140" s="2">
         <v>53200942899</v>
       </c>
-      <c r="Y140" s="2">
+      <c r="Y140" s="7">
         <v>49862265601.459999</v>
       </c>
-      <c r="Z140" s="2">
+      <c r="Z140" s="7">
         <v>49815877000</v>
       </c>
       <c r="AA140" s="3">
-        <v>52825824907.282104</v>
+        <v>52865495367.134308</v>
       </c>
       <c r="AB140" s="3">
-        <v>53756050910.666107</v>
+        <v>53841830901.108047</v>
       </c>
       <c r="AC140" s="3">
-        <v>53699025216.524033</v>
+        <v>53832434835.844604</v>
       </c>
       <c r="AD140" s="3">
-        <v>54814885354.674393</v>
+        <v>54997059000.872986</v>
       </c>
       <c r="AE140" s="3">
-        <v>56281489382.63974</v>
+        <v>56515043056.519905</v>
       </c>
       <c r="AF140" s="3">
-        <v>57536685763.207016</v>
+        <v>57823605967.084122</v>
       </c>
       <c r="AG140" s="3">
-        <v>58661705367.759544</v>
+        <v>59003741203.478409</v>
       </c>
     </row>
     <row r="141" spans="1:33" x14ac:dyDescent="0.25">
@@ -16496,32 +16504,32 @@
       <c r="X141" s="2">
         <v>153999783</v>
       </c>
-      <c r="Y141" s="2">
+      <c r="Y141" s="7">
         <v>153674342.13999999</v>
       </c>
-      <c r="Z141" s="2">
+      <c r="Z141" s="7">
         <v>171772000</v>
       </c>
       <c r="AA141" s="3">
-        <v>154238444.42213452</v>
+        <v>153218726.18285242</v>
       </c>
       <c r="AB141" s="3">
-        <v>148671265.29270136</v>
+        <v>146742732.38557488</v>
       </c>
       <c r="AC141" s="3">
-        <v>147582819.62676796</v>
+        <v>144747698.67973763</v>
       </c>
       <c r="AD141" s="3">
-        <v>141534730.30889472</v>
+        <v>137924976.83582211</v>
       </c>
       <c r="AE141" s="3">
-        <v>134431043.97761574</v>
+        <v>130158164.68177502</v>
       </c>
       <c r="AF141" s="3">
-        <v>128606555.87838578</v>
+        <v>123718865.69108997</v>
       </c>
       <c r="AG141" s="3">
-        <v>123579289.22763473</v>
+        <v>118120425.09144168</v>
       </c>
     </row>
     <row r="142" spans="1:33" x14ac:dyDescent="0.25">
@@ -16597,10 +16605,10 @@
       <c r="X142" s="2">
         <v>104148171</v>
       </c>
-      <c r="Y142" s="2">
+      <c r="Y142" s="7">
         <v>105260526.01000001</v>
       </c>
-      <c r="Z142" s="2">
+      <c r="Z142" s="7">
         <v>109999000</v>
       </c>
       <c r="AA142" s="3">
@@ -16698,10 +16706,10 @@
       <c r="X143" s="2">
         <v>162596965</v>
       </c>
-      <c r="Y143" s="2">
+      <c r="Y143" s="7">
         <v>177332898.46000001</v>
       </c>
-      <c r="Z143" s="2">
+      <c r="Z143" s="7">
         <v>186584000</v>
       </c>
       <c r="AA143" s="3">
@@ -16799,10 +16807,10 @@
       <c r="X144" s="2">
         <v>7763216930</v>
       </c>
-      <c r="Y144" s="2">
+      <c r="Y144" s="7">
         <v>8261150660.4799995</v>
       </c>
-      <c r="Z144" s="2">
+      <c r="Z144" s="7">
         <v>8341650000</v>
       </c>
       <c r="AA144" s="3">
@@ -16900,10 +16908,10 @@
       <c r="X145" s="2">
         <v>1291138707</v>
       </c>
-      <c r="Y145" s="2">
+      <c r="Y145" s="7">
         <v>1294749937.6900001</v>
       </c>
-      <c r="Z145" s="2">
+      <c r="Z145" s="7">
         <v>1404150000</v>
       </c>
       <c r="AA145" s="3">
@@ -17001,10 +17009,10 @@
       <c r="X146" s="2">
         <v>69800756</v>
       </c>
-      <c r="Y146" s="2">
+      <c r="Y146" s="7">
         <v>90161953.969999999</v>
       </c>
-      <c r="Z146" s="2">
+      <c r="Z146" s="7">
         <v>108719000</v>
       </c>
       <c r="AA146" s="3">
@@ -17102,32 +17110,32 @@
       <c r="X147" s="2">
         <v>524994594</v>
       </c>
-      <c r="Y147" s="2">
+      <c r="Y147" s="7">
         <v>574778895.84000003</v>
       </c>
-      <c r="Z147" s="2">
+      <c r="Z147" s="7">
         <v>536261000</v>
       </c>
       <c r="AA147" s="3">
-        <v>571313514.78801548</v>
+        <v>574943535.16508603</v>
       </c>
       <c r="AB147" s="3">
-        <v>597724108.49021518</v>
+        <v>602729837.92342556</v>
       </c>
       <c r="AC147" s="3">
-        <v>620367331.20853114</v>
+        <v>625601938.16447139</v>
       </c>
       <c r="AD147" s="3">
-        <v>649924785.25702167</v>
+        <v>656939408.37868178</v>
       </c>
       <c r="AE147" s="3">
-        <v>682626520.31901622</v>
+        <v>692029429.59678328</v>
       </c>
       <c r="AF147" s="3">
-        <v>715614794.92322576</v>
+        <v>727280105.45916867</v>
       </c>
       <c r="AG147" s="3">
-        <v>749317894.55545723</v>
+        <v>763214694.72730756</v>
       </c>
     </row>
     <row r="148" spans="1:33" x14ac:dyDescent="0.25">
@@ -17203,10 +17211,10 @@
       <c r="X148" s="2">
         <v>494327301</v>
       </c>
-      <c r="Y148" s="2">
+      <c r="Y148" s="7">
         <v>456936409.06</v>
       </c>
-      <c r="Z148" s="2">
+      <c r="Z148" s="7">
         <v>481730000</v>
       </c>
       <c r="AA148" s="3">
@@ -17304,10 +17312,10 @@
       <c r="X149" s="2">
         <v>491941949</v>
       </c>
-      <c r="Y149" s="2">
+      <c r="Y149" s="7">
         <v>411463204.44999999</v>
       </c>
-      <c r="Z149" s="2">
+      <c r="Z149" s="7">
         <v>466724000</v>
       </c>
       <c r="AA149" s="3">
@@ -17405,10 +17413,10 @@
       <c r="X150" s="2">
         <v>141380198</v>
       </c>
-      <c r="Y150" s="2">
+      <c r="Y150" s="7">
         <v>168406981.15000001</v>
       </c>
-      <c r="Z150" s="2">
+      <c r="Z150" s="7">
         <v>169622000</v>
       </c>
       <c r="AA150" s="3">
@@ -17506,10 +17514,10 @@
       <c r="X151" s="2">
         <v>179308592</v>
       </c>
-      <c r="Y151" s="2">
+      <c r="Y151" s="7">
         <v>178251017.84999999</v>
       </c>
-      <c r="Z151" s="2">
+      <c r="Z151" s="7">
         <v>201026000</v>
       </c>
       <c r="AA151" s="3">
@@ -17607,32 +17615,32 @@
       <c r="X152" s="2">
         <v>550269174</v>
       </c>
-      <c r="Y152" s="2">
+      <c r="Y152" s="7">
         <v>578932345.26999998</v>
       </c>
-      <c r="Z152" s="2">
+      <c r="Z152" s="7">
         <v>579987000</v>
       </c>
       <c r="AA152" s="3">
-        <v>606486705.54632568</v>
+        <v>607748668.0388304</v>
       </c>
       <c r="AB152" s="3">
-        <v>630290088.61706305</v>
+        <v>632027555.91295803</v>
       </c>
       <c r="AC152" s="3">
-        <v>653256970.78167629</v>
+        <v>655094213.62570238</v>
       </c>
       <c r="AD152" s="3">
-        <v>679207659.35471797</v>
+        <v>681648603.7992264</v>
       </c>
       <c r="AE152" s="3">
-        <v>706799981.00366819</v>
+        <v>710032648.26943374</v>
       </c>
       <c r="AF152" s="3">
-        <v>735039567.81530523</v>
+        <v>739013854.25635588</v>
       </c>
       <c r="AG152" s="3">
-        <v>764103384.79426491</v>
+        <v>768802285.19224691</v>
       </c>
     </row>
     <row r="153" spans="1:33" x14ac:dyDescent="0.25">
@@ -17708,32 +17716,32 @@
       <c r="X153" s="2">
         <v>935698846</v>
       </c>
-      <c r="Y153" s="2">
+      <c r="Y153" s="7">
         <v>1027142237.65</v>
       </c>
-      <c r="Z153" s="2">
+      <c r="Z153" s="7">
         <v>1138042000</v>
       </c>
       <c r="AA153" s="3">
-        <v>1207913968.7504256</v>
+        <v>1200559808.5494871</v>
       </c>
       <c r="AB153" s="3">
-        <v>1249561257.7279391</v>
+        <v>1244319498.4708164</v>
       </c>
       <c r="AC153" s="3">
-        <v>1277976184.362642</v>
+        <v>1279643424.3269961</v>
       </c>
       <c r="AD153" s="3">
-        <v>1324586767.5245836</v>
+        <v>1328037465.84904</v>
       </c>
       <c r="AE153" s="3">
-        <v>1377874059.9920983</v>
+        <v>1381688212.6968927</v>
       </c>
       <c r="AF153" s="3">
-        <v>1429446887.2124054</v>
+        <v>1434849543.214905</v>
       </c>
       <c r="AG153" s="3">
-        <v>1480479329.3638976</v>
+        <v>1488353182.5788295</v>
       </c>
     </row>
     <row r="154" spans="1:33" x14ac:dyDescent="0.25">
@@ -17809,10 +17817,10 @@
       <c r="X154" s="2">
         <v>345817014</v>
       </c>
-      <c r="Y154" s="2">
+      <c r="Y154" s="7">
         <v>356689384.64999998</v>
       </c>
-      <c r="Z154" s="2">
+      <c r="Z154" s="7">
         <v>346309000</v>
       </c>
       <c r="AA154" s="3">
@@ -17910,10 +17918,10 @@
       <c r="X155" s="2">
         <v>69810198</v>
       </c>
-      <c r="Y155" s="2">
+      <c r="Y155" s="7">
         <v>73666481.890000001</v>
       </c>
-      <c r="Z155" s="2">
+      <c r="Z155" s="7">
         <v>70008000</v>
       </c>
       <c r="AA155" s="3">
@@ -18011,32 +18019,32 @@
       <c r="X156" s="2">
         <v>2939172564</v>
       </c>
-      <c r="Y156" s="2">
+      <c r="Y156" s="7">
         <v>3314625752.2399998</v>
       </c>
-      <c r="Z156" s="2">
+      <c r="Z156" s="7">
         <v>3296812000</v>
       </c>
       <c r="AA156" s="3">
-        <v>3393004660.8667421</v>
+        <v>3394564968.2835946</v>
       </c>
       <c r="AB156" s="3">
-        <v>3434214083.6376028</v>
+        <v>3436964515.4991136</v>
       </c>
       <c r="AC156" s="3">
-        <v>3450416091.9603543</v>
+        <v>3454173056.161438</v>
       </c>
       <c r="AD156" s="3">
-        <v>3496675033.3797698</v>
+        <v>3501706916.8696642</v>
       </c>
       <c r="AE156" s="3">
-        <v>3551866880.4061275</v>
+        <v>3558282280.1410551</v>
       </c>
       <c r="AF156" s="3">
-        <v>3601636922.5557103</v>
+        <v>3609419903.3942661</v>
       </c>
       <c r="AG156" s="3">
-        <v>3648165410.6711354</v>
+        <v>3657315258.8349071</v>
       </c>
     </row>
     <row r="157" spans="1:33" x14ac:dyDescent="0.25">
@@ -18112,10 +18120,10 @@
       <c r="X157" s="2">
         <v>73347506</v>
       </c>
-      <c r="Y157" s="2">
+      <c r="Y157" s="7">
         <v>80717814.140000001</v>
       </c>
-      <c r="Z157" s="2">
+      <c r="Z157" s="7">
         <v>86474000</v>
       </c>
       <c r="AA157" s="3">
@@ -18213,32 +18221,32 @@
       <c r="X158" s="2">
         <v>354461407</v>
       </c>
-      <c r="Y158" s="2">
+      <c r="Y158" s="7">
         <v>386272988.32999998</v>
       </c>
-      <c r="Z158" s="2">
+      <c r="Z158" s="7">
         <v>417209000</v>
       </c>
       <c r="AA158" s="3">
-        <v>408716622.80117065</v>
+        <v>408152596.92833412</v>
       </c>
       <c r="AB158" s="3">
-        <v>417853675.89422071</v>
+        <v>416922503.19698572</v>
       </c>
       <c r="AC158" s="3">
-        <v>434977883.21444345</v>
+        <v>433734259.65621364</v>
       </c>
       <c r="AD158" s="3">
-        <v>443326150.65249807</v>
+        <v>441666376.8093428</v>
       </c>
       <c r="AE158" s="3">
-        <v>449191743.27646643</v>
+        <v>447080761.09219843</v>
       </c>
       <c r="AF158" s="3">
-        <v>457130659.9260782</v>
+        <v>454570333.46586108</v>
       </c>
       <c r="AG158" s="3">
-        <v>466463576.56225789</v>
+        <v>463446145.76381046</v>
       </c>
     </row>
     <row r="159" spans="1:33" x14ac:dyDescent="0.25">
@@ -18314,10 +18322,10 @@
       <c r="X159" s="2">
         <v>322312859</v>
       </c>
-      <c r="Y159" s="2">
+      <c r="Y159" s="7">
         <v>349788150.68000001</v>
       </c>
-      <c r="Z159" s="2">
+      <c r="Z159" s="7">
         <v>355365000</v>
       </c>
       <c r="AA159" s="3">
@@ -18415,10 +18423,10 @@
       <c r="X160" s="2">
         <v>2117638951</v>
       </c>
-      <c r="Y160" s="2">
+      <c r="Y160" s="7">
         <v>2465455152.4400001</v>
       </c>
-      <c r="Z160" s="2">
+      <c r="Z160" s="7">
         <v>2499223000</v>
       </c>
       <c r="AA160" s="3">
@@ -18516,10 +18524,10 @@
       <c r="X161" s="2">
         <v>114855698</v>
       </c>
-      <c r="Y161" s="2">
+      <c r="Y161" s="7">
         <v>109754709.48999999</v>
       </c>
-      <c r="Z161" s="2">
+      <c r="Z161" s="7">
         <v>111255000</v>
       </c>
       <c r="AA161" s="3">
@@ -18617,32 +18625,32 @@
       <c r="X162" s="2">
         <v>887424091</v>
       </c>
-      <c r="Y162" s="2">
+      <c r="Y162" s="7">
         <v>953204045</v>
       </c>
-      <c r="Z162" s="2">
+      <c r="Z162" s="7">
         <v>1050211000</v>
       </c>
       <c r="AA162" s="3">
-        <v>1078846293.4398558</v>
+        <v>1077711004.0192485</v>
       </c>
       <c r="AB162" s="3">
-        <v>1105718368.885962</v>
+        <v>1104580378.1847281</v>
       </c>
       <c r="AC162" s="3">
-        <v>1132122723.6696849</v>
+        <v>1131515928.209594</v>
       </c>
       <c r="AD162" s="3">
-        <v>1160519524.520848</v>
+        <v>1159831787.2182562</v>
       </c>
       <c r="AE162" s="3">
-        <v>1190010566.7617111</v>
+        <v>1189059141.3054957</v>
       </c>
       <c r="AF162" s="3">
-        <v>1219959130.6438551</v>
+        <v>1218867990.6966488</v>
       </c>
       <c r="AG162" s="3">
-        <v>1250476678.7332454</v>
+        <v>1249326034.2412529</v>
       </c>
     </row>
     <row r="163" spans="1:33" x14ac:dyDescent="0.25">
@@ -18718,10 +18726,10 @@
       <c r="X163" s="2">
         <v>73873912</v>
       </c>
-      <c r="Y163" s="2">
+      <c r="Y163" s="7">
         <v>73370667.769999996</v>
       </c>
-      <c r="Z163" s="2">
+      <c r="Z163" s="7">
         <v>77764000</v>
       </c>
       <c r="AA163" s="3">
@@ -18819,10 +18827,10 @@
       <c r="X164" s="2">
         <v>401751805</v>
       </c>
-      <c r="Y164" s="2">
+      <c r="Y164" s="7">
         <v>413961190.38999999</v>
       </c>
-      <c r="Z164" s="2">
+      <c r="Z164" s="7">
         <v>469316000</v>
       </c>
       <c r="AA164" s="3">
@@ -18920,32 +18928,32 @@
       <c r="X165" s="2">
         <v>105569232</v>
       </c>
-      <c r="Y165" s="2">
+      <c r="Y165" s="7">
         <v>105649466.81</v>
       </c>
-      <c r="Z165" s="2">
+      <c r="Z165" s="7">
         <v>106937000</v>
       </c>
       <c r="AA165" s="3">
-        <v>106921174.93625055</v>
+        <v>107027698.90391162</v>
       </c>
       <c r="AB165" s="3">
-        <v>108376290.70840049</v>
+        <v>108361262.67721741</v>
       </c>
       <c r="AC165" s="3">
-        <v>110501406.97864699</v>
+        <v>110260168.09486425</v>
       </c>
       <c r="AD165" s="3">
-        <v>111892664.23502205</v>
+        <v>111539189.96818961</v>
       </c>
       <c r="AE165" s="3">
-        <v>113086579.2776242</v>
+        <v>112652269.16846366</v>
       </c>
       <c r="AF165" s="3">
-        <v>114455068.64914975</v>
+        <v>113912528.93284459</v>
       </c>
       <c r="AG165" s="3">
-        <v>115941224.91074745</v>
+        <v>115271822.17959058</v>
       </c>
     </row>
     <row r="166" spans="1:33" x14ac:dyDescent="0.25">
@@ -19021,10 +19029,10 @@
       <c r="X166" s="2">
         <v>201009275</v>
       </c>
-      <c r="Y166" s="2">
+      <c r="Y166" s="7">
         <v>197028641.12</v>
       </c>
-      <c r="Z166" s="2">
+      <c r="Z166" s="7">
         <v>203356000</v>
       </c>
       <c r="AA166" s="3">
@@ -19122,10 +19130,10 @@
       <c r="X167" s="2">
         <v>1285551247</v>
       </c>
-      <c r="Y167" s="2">
+      <c r="Y167" s="7">
         <v>1239939962.8199999</v>
       </c>
-      <c r="Z167" s="2">
+      <c r="Z167" s="7">
         <v>1249317000</v>
       </c>
       <c r="AA167" s="3">
@@ -19223,10 +19231,10 @@
       <c r="X168" s="2">
         <v>275509917</v>
       </c>
-      <c r="Y168" s="2">
+      <c r="Y168" s="7">
         <v>273105460.32999998</v>
       </c>
-      <c r="Z168" s="2">
+      <c r="Z168" s="7">
         <v>325033000</v>
       </c>
       <c r="AA168" s="3">
@@ -19324,32 +19332,32 @@
       <c r="X169" s="2">
         <v>280242852</v>
       </c>
-      <c r="Y169" s="2">
+      <c r="Y169" s="7">
         <v>287898357.76999998</v>
       </c>
-      <c r="Z169" s="2">
+      <c r="Z169" s="7">
         <v>285959000</v>
       </c>
       <c r="AA169" s="3">
-        <v>304587617.4216693</v>
+        <v>304859072.30268198</v>
       </c>
       <c r="AB169" s="3">
-        <v>310549322.36704952</v>
+        <v>311105488.05276239</v>
       </c>
       <c r="AC169" s="3">
-        <v>310456049.20463669</v>
+        <v>311292720.45444566</v>
       </c>
       <c r="AD169" s="3">
-        <v>317580384.98455781</v>
+        <v>318722306.17986971</v>
       </c>
       <c r="AE169" s="3">
-        <v>326888277.34570622</v>
+        <v>328358003.09142482</v>
       </c>
       <c r="AF169" s="3">
-        <v>334919365.10429072</v>
+        <v>336727313.92330289</v>
       </c>
       <c r="AG169" s="3">
-        <v>342167720.31960887</v>
+        <v>344323902.6048584</v>
       </c>
     </row>
     <row r="170" spans="1:33" x14ac:dyDescent="0.25">
@@ -19425,10 +19433,10 @@
       <c r="X170" s="2">
         <v>1088919642</v>
       </c>
-      <c r="Y170" s="2">
+      <c r="Y170" s="7">
         <v>1007590019.62</v>
       </c>
-      <c r="Z170" s="2">
+      <c r="Z170" s="7">
         <v>1019641000</v>
       </c>
       <c r="AA170" s="3">
@@ -19526,10 +19534,10 @@
       <c r="X171" s="2">
         <v>171294470</v>
       </c>
-      <c r="Y171" s="2">
+      <c r="Y171" s="7">
         <v>190678497.91</v>
       </c>
-      <c r="Z171" s="2">
+      <c r="Z171" s="7">
         <v>194418000</v>
       </c>
       <c r="AA171" s="3">
@@ -19627,32 +19635,32 @@
       <c r="X172" s="2">
         <v>7250512622</v>
       </c>
-      <c r="Y172" s="2">
+      <c r="Y172" s="7">
         <v>7851457958.3400002</v>
       </c>
-      <c r="Z172" s="2">
+      <c r="Z172" s="7">
         <v>7939674000</v>
       </c>
       <c r="AA172" s="3">
-        <v>8882840204.5939293</v>
+        <v>8895713930.2784615</v>
       </c>
       <c r="AB172" s="3">
-        <v>9551639501.6616096</v>
+        <v>9600423061.4380951</v>
       </c>
       <c r="AC172" s="3">
-        <v>10089596319.708677</v>
+        <v>10188491908.462831</v>
       </c>
       <c r="AD172" s="3">
-        <v>10881757937.079891</v>
+        <v>11026696172.753895</v>
       </c>
       <c r="AE172" s="3">
-        <v>11802185612.939659</v>
+        <v>11997260881.849154</v>
       </c>
       <c r="AF172" s="3">
-        <v>12747061624.247398</v>
+        <v>13001844293.203291</v>
       </c>
       <c r="AG172" s="3">
-        <v>13731978409.882481</v>
+        <v>14056154286.265085</v>
       </c>
     </row>
     <row r="173" spans="1:33" x14ac:dyDescent="0.25">
@@ -19728,10 +19736,10 @@
       <c r="X173" s="2">
         <v>293155148</v>
       </c>
-      <c r="Y173" s="2">
+      <c r="Y173" s="7">
         <v>279910280.80000001</v>
       </c>
-      <c r="Z173" s="2">
+      <c r="Z173" s="7">
         <v>266502000</v>
       </c>
       <c r="AA173" s="3">
@@ -19829,10 +19837,10 @@
       <c r="X174" s="2">
         <v>223591629</v>
       </c>
-      <c r="Y174" s="2">
+      <c r="Y174" s="7">
         <v>183429956.25</v>
       </c>
-      <c r="Z174" s="2">
+      <c r="Z174" s="7">
         <v>191952000</v>
       </c>
       <c r="AA174" s="3">
@@ -19930,10 +19938,10 @@
       <c r="X175" s="2">
         <v>816235323</v>
       </c>
-      <c r="Y175" s="2">
+      <c r="Y175" s="7">
         <v>905327076.73000002</v>
       </c>
-      <c r="Z175" s="2">
+      <c r="Z175" s="7">
         <v>972888000</v>
       </c>
       <c r="AA175" s="3">
@@ -20031,10 +20039,10 @@
       <c r="X176" s="2">
         <v>1268343902</v>
       </c>
-      <c r="Y176" s="2">
+      <c r="Y176" s="7">
         <v>1276544221.73</v>
       </c>
-      <c r="Z176" s="2">
+      <c r="Z176" s="7">
         <v>1333549000</v>
       </c>
       <c r="AA176" s="3">
@@ -20132,10 +20140,10 @@
       <c r="X177" s="2">
         <v>141449834</v>
       </c>
-      <c r="Y177" s="2">
+      <c r="Y177" s="7">
         <v>153634900.25</v>
       </c>
-      <c r="Z177" s="2">
+      <c r="Z177" s="7">
         <v>160908000</v>
       </c>
       <c r="AA177" s="3">
@@ -20233,10 +20241,10 @@
       <c r="X178" s="2">
         <v>1402228122</v>
       </c>
-      <c r="Y178" s="2">
+      <c r="Y178" s="7">
         <v>1395748549.0899999</v>
       </c>
-      <c r="Z178" s="2">
+      <c r="Z178" s="7">
         <v>1408944000</v>
       </c>
       <c r="AA178" s="3">
@@ -20334,10 +20342,10 @@
       <c r="X179" s="2">
         <v>1178040450</v>
       </c>
-      <c r="Y179" s="2">
+      <c r="Y179" s="7">
         <v>1212977053.1700001</v>
       </c>
-      <c r="Z179" s="2">
+      <c r="Z179" s="7">
         <v>1267788000</v>
       </c>
       <c r="AA179" s="3">
@@ -20435,10 +20443,10 @@
       <c r="X180" s="2">
         <v>298176071</v>
       </c>
-      <c r="Y180" s="2">
+      <c r="Y180" s="7">
         <v>285992000.07999998</v>
       </c>
-      <c r="Z180" s="2">
+      <c r="Z180" s="7">
         <v>307202000</v>
       </c>
       <c r="AA180" s="3">
@@ -20536,10 +20544,10 @@
       <c r="X181" s="2">
         <v>162012725</v>
       </c>
-      <c r="Y181" s="2">
+      <c r="Y181" s="7">
         <v>194194303.56</v>
       </c>
-      <c r="Z181" s="2">
+      <c r="Z181" s="7">
         <v>170820000</v>
       </c>
       <c r="AA181" s="3">
@@ -20637,10 +20645,10 @@
       <c r="X182" s="2">
         <v>68827022</v>
       </c>
-      <c r="Y182" s="2">
+      <c r="Y182" s="7">
         <v>81539520.040000007</v>
       </c>
-      <c r="Z182" s="2">
+      <c r="Z182" s="7">
         <v>73788000</v>
       </c>
       <c r="AA182" s="3">
@@ -20738,10 +20746,10 @@
       <c r="X183" s="2">
         <v>100254417</v>
       </c>
-      <c r="Y183" s="2">
+      <c r="Y183" s="7">
         <v>102542322.89</v>
       </c>
-      <c r="Z183" s="2">
+      <c r="Z183" s="7">
         <v>111006000</v>
       </c>
       <c r="AA183" s="3">
@@ -20839,10 +20847,10 @@
       <c r="X184" s="2">
         <v>9690167000</v>
       </c>
-      <c r="Y184" s="2">
+      <c r="Y184" s="7">
         <v>9975842711.9200001</v>
       </c>
-      <c r="Z184" s="2">
+      <c r="Z184" s="7">
         <v>10294550000</v>
       </c>
       <c r="AA184" s="3">
@@ -20940,10 +20948,10 @@
       <c r="X185" s="2">
         <v>392192693</v>
       </c>
-      <c r="Y185" s="2">
+      <c r="Y185" s="7">
         <v>362405170.89999998</v>
       </c>
-      <c r="Z185" s="2">
+      <c r="Z185" s="7">
         <v>361215000</v>
       </c>
       <c r="AA185" s="3">
@@ -21041,10 +21049,10 @@
       <c r="X186" s="2">
         <v>221771633</v>
       </c>
-      <c r="Y186" s="2">
+      <c r="Y186" s="7">
         <v>198326936.44</v>
       </c>
-      <c r="Z186" s="2">
+      <c r="Z186" s="7">
         <v>205053000</v>
       </c>
       <c r="AA186" s="3">
@@ -21142,10 +21150,10 @@
       <c r="X187" s="2">
         <v>1078557938</v>
       </c>
-      <c r="Y187" s="2">
+      <c r="Y187" s="7">
         <v>1118979376.05</v>
       </c>
-      <c r="Z187" s="2">
+      <c r="Z187" s="7">
         <v>1211264000</v>
       </c>
       <c r="AA187" s="3">
@@ -21243,32 +21251,32 @@
       <c r="X188" s="2">
         <v>1007756302</v>
       </c>
-      <c r="Y188" s="2">
+      <c r="Y188" s="7">
         <v>1149048334.01</v>
       </c>
-      <c r="Z188" s="2">
+      <c r="Z188" s="7">
         <v>1183058000</v>
       </c>
       <c r="AA188" s="3">
-        <v>1248574307.3344533</v>
+        <v>1248906695.295588</v>
       </c>
       <c r="AB188" s="3">
-        <v>1273577996.5466769</v>
+        <v>1274793065.4521039</v>
       </c>
       <c r="AC188" s="3">
-        <v>1279447360.8832016</v>
+        <v>1281795967.1177871</v>
       </c>
       <c r="AD188" s="3">
-        <v>1308419129.8269091</v>
+        <v>1311680097.2715063</v>
       </c>
       <c r="AE188" s="3">
-        <v>1344503380.9655836</v>
+        <v>1348656509.4159119</v>
       </c>
       <c r="AF188" s="3">
-        <v>1376638323.8202991</v>
+        <v>1381774548.7681963</v>
       </c>
       <c r="AG188" s="3">
-        <v>1406416258.3972485</v>
+        <v>1412606428.0464666</v>
       </c>
     </row>
     <row r="189" spans="1:33" x14ac:dyDescent="0.25">
@@ -21344,10 +21352,10 @@
       <c r="X189" s="2">
         <v>169135732</v>
       </c>
-      <c r="Y189" s="2">
+      <c r="Y189" s="7">
         <v>202277698.41999999</v>
       </c>
-      <c r="Z189" s="2">
+      <c r="Z189" s="7">
         <v>194244000</v>
       </c>
       <c r="AA189" s="3">
@@ -21445,10 +21453,10 @@
       <c r="X190" s="2">
         <v>280161412</v>
       </c>
-      <c r="Y190" s="2">
+      <c r="Y190" s="7">
         <v>301172742.70999998</v>
       </c>
-      <c r="Z190" s="2">
+      <c r="Z190" s="7">
         <v>301934000</v>
       </c>
       <c r="AA190" s="3">
@@ -21546,10 +21554,10 @@
       <c r="X191" s="2">
         <v>206767875</v>
       </c>
-      <c r="Y191" s="2">
+      <c r="Y191" s="7">
         <v>192200297.24000001</v>
       </c>
-      <c r="Z191" s="2">
+      <c r="Z191" s="7">
         <v>218824000</v>
       </c>
       <c r="AA191" s="3">
@@ -21647,10 +21655,10 @@
       <c r="X192" s="2">
         <v>295156908</v>
       </c>
-      <c r="Y192" s="2">
+      <c r="Y192" s="7">
         <v>327804778.79000002</v>
       </c>
-      <c r="Z192" s="2">
+      <c r="Z192" s="7">
         <v>417795000</v>
       </c>
       <c r="AA192" s="3">
@@ -21748,10 +21756,10 @@
       <c r="X193" s="2">
         <v>287907609</v>
       </c>
-      <c r="Y193" s="2">
+      <c r="Y193" s="7">
         <v>313348232.95999998</v>
       </c>
-      <c r="Z193" s="2">
+      <c r="Z193" s="7">
         <v>305366000</v>
       </c>
       <c r="AA193" s="3">
@@ -21849,32 +21857,32 @@
       <c r="X194" s="2">
         <v>1224134042</v>
       </c>
-      <c r="Y194" s="2">
+      <c r="Y194" s="7">
         <v>1256903259.46</v>
       </c>
-      <c r="Z194" s="2">
+      <c r="Z194" s="7">
         <v>1340663000</v>
       </c>
       <c r="AA194" s="3">
-        <v>1403480128.8127587</v>
+        <v>1401757447.0687211</v>
       </c>
       <c r="AB194" s="3">
-        <v>1468599966.2118573</v>
+        <v>1466742721.8213041</v>
       </c>
       <c r="AC194" s="3">
-        <v>1536448961.7033713</v>
+        <v>1535245719.8858883</v>
       </c>
       <c r="AD194" s="3">
-        <v>1607790334.3496389</v>
+        <v>1606329723.8838637</v>
       </c>
       <c r="AE194" s="3">
-        <v>1682546706.4767609</v>
+        <v>1680527994.42766</v>
       </c>
       <c r="AF194" s="3">
-        <v>1760699088.5167668</v>
+        <v>1758291592.3993447</v>
       </c>
       <c r="AG194" s="3">
-        <v>1842429955.999913</v>
+        <v>1839742710.0291445</v>
       </c>
     </row>
     <row r="195" spans="1:33" x14ac:dyDescent="0.25">
@@ -21950,10 +21958,10 @@
       <c r="X195" s="2">
         <v>142763489</v>
       </c>
-      <c r="Y195" s="2">
+      <c r="Y195" s="7">
         <v>159314531.44999999</v>
       </c>
-      <c r="Z195" s="2">
+      <c r="Z195" s="7">
         <v>166701000</v>
       </c>
       <c r="AA195" s="3">
@@ -22051,32 +22059,32 @@
       <c r="X196" s="2">
         <v>141006048</v>
       </c>
-      <c r="Y196" s="2">
+      <c r="Y196" s="7">
         <v>151769080.05000001</v>
       </c>
-      <c r="Z196" s="2">
+      <c r="Z196" s="7">
         <v>164483000</v>
       </c>
       <c r="AA196" s="3">
-        <v>174368341.6040864</v>
+        <v>170795776.15263888</v>
       </c>
       <c r="AB196" s="3">
-        <v>179881801.11926019</v>
+        <v>173874735.72290844</v>
       </c>
       <c r="AC196" s="3">
-        <v>183381734.37239063</v>
+        <v>175465966.94925299</v>
       </c>
       <c r="AD196" s="3">
-        <v>189856283.57942152</v>
+        <v>178893589.50048164</v>
       </c>
       <c r="AE196" s="3">
-        <v>197494061.46897787</v>
+        <v>182896363.36723977</v>
       </c>
       <c r="AF196" s="3">
-        <v>204996261.80753207</v>
+        <v>186601486.34224123</v>
       </c>
       <c r="AG196" s="3">
-        <v>212567119.94983378</v>
+        <v>190137806.49656799</v>
       </c>
     </row>
     <row r="197" spans="1:33" x14ac:dyDescent="0.25">
@@ -22152,32 +22160,32 @@
       <c r="X197" s="2">
         <v>263868786</v>
       </c>
-      <c r="Y197" s="2">
+      <c r="Y197" s="7">
         <v>270753190.23000002</v>
       </c>
-      <c r="Z197" s="2">
+      <c r="Z197" s="7">
         <v>265682000</v>
       </c>
       <c r="AA197" s="3">
-        <v>266475097.67278734</v>
+        <v>267201063.71183887</v>
       </c>
       <c r="AB197" s="3">
-        <v>269684213.21621323</v>
+        <v>270250915.5853228</v>
       </c>
       <c r="AC197" s="3">
-        <v>273997230.3155849</v>
+        <v>274006935.14637715</v>
       </c>
       <c r="AD197" s="3">
-        <v>277113137.19691926</v>
+        <v>277018874.30836147</v>
       </c>
       <c r="AE197" s="3">
-        <v>279914133.72056687</v>
+        <v>279843661.2783739</v>
       </c>
       <c r="AF197" s="3">
-        <v>283007180.41128486</v>
+        <v>282863078.6083805</v>
       </c>
       <c r="AG197" s="3">
-        <v>286299004.61472613</v>
+        <v>286018539.81042147</v>
       </c>
     </row>
     <row r="198" spans="1:33" x14ac:dyDescent="0.25">
@@ -22253,10 +22261,10 @@
       <c r="X198" s="2">
         <v>1787206925</v>
       </c>
-      <c r="Y198" s="2">
+      <c r="Y198" s="7">
         <v>1905041866.99</v>
       </c>
-      <c r="Z198" s="2">
+      <c r="Z198" s="7">
         <v>1941701000</v>
       </c>
       <c r="AA198" s="3">
@@ -22354,10 +22362,10 @@
       <c r="X199" s="2">
         <v>268257078</v>
       </c>
-      <c r="Y199" s="2">
+      <c r="Y199" s="7">
         <v>264954137.78</v>
       </c>
-      <c r="Z199" s="2">
+      <c r="Z199" s="7">
         <v>323209000</v>
       </c>
       <c r="AA199" s="3">
@@ -22455,10 +22463,10 @@
       <c r="X200" s="2">
         <v>945594338</v>
       </c>
-      <c r="Y200" s="2">
+      <c r="Y200" s="7">
         <v>459951521.91000003</v>
       </c>
-      <c r="Z200" s="2">
+      <c r="Z200" s="7">
         <v>953671000</v>
       </c>
       <c r="AA200" s="3">
@@ -22556,10 +22564,10 @@
       <c r="X201" s="2">
         <v>167523466</v>
       </c>
-      <c r="Y201" s="2">
+      <c r="Y201" s="7">
         <v>167551311.40000001</v>
       </c>
-      <c r="Z201" s="2">
+      <c r="Z201" s="7">
         <v>144007000</v>
       </c>
       <c r="AA201" s="3">
@@ -22657,32 +22665,32 @@
       <c r="X202" s="2">
         <v>3312408732</v>
       </c>
-      <c r="Y202" s="2">
+      <c r="Y202" s="7">
         <v>3247513196.6199999</v>
       </c>
-      <c r="Z202" s="2">
+      <c r="Z202" s="7">
         <v>3184672000</v>
       </c>
       <c r="AA202" s="3">
-        <v>3503489796.8159461</v>
+        <v>3497478324.6959963</v>
       </c>
       <c r="AB202" s="3">
-        <v>3588420813.9364967</v>
+        <v>3605206960.6042461</v>
       </c>
       <c r="AC202" s="3">
-        <v>3556685306.4602532</v>
+        <v>3610254432.5272069</v>
       </c>
       <c r="AD202" s="3">
-        <v>3662889712.7959332</v>
+        <v>3739482970.3080001</v>
       </c>
       <c r="AE202" s="3">
-        <v>3811054069.7435837</v>
+        <v>3908527697.8738904</v>
       </c>
       <c r="AF202" s="3">
-        <v>3935134597.7445421</v>
+        <v>4057802397.6045303</v>
       </c>
       <c r="AG202" s="3">
-        <v>4044084477.8786945</v>
+        <v>4195211231.1537118</v>
       </c>
     </row>
     <row r="203" spans="1:33" x14ac:dyDescent="0.25">
@@ -22758,10 +22766,10 @@
       <c r="X203" s="2">
         <v>207465422</v>
       </c>
-      <c r="Y203" s="2">
+      <c r="Y203" s="7">
         <v>187518764.81999999</v>
       </c>
-      <c r="Z203" s="2">
+      <c r="Z203" s="7">
         <v>205504000</v>
       </c>
       <c r="AA203" s="3">
@@ -22859,10 +22867,10 @@
       <c r="X204" s="2">
         <v>196683537</v>
       </c>
-      <c r="Y204" s="2">
+      <c r="Y204" s="7">
         <v>168077203.18000001</v>
       </c>
-      <c r="Z204" s="2">
+      <c r="Z204" s="7">
         <v>158355000</v>
       </c>
       <c r="AA204" s="3">
@@ -22960,10 +22968,10 @@
       <c r="X205" s="2">
         <v>343550871</v>
       </c>
-      <c r="Y205" s="2">
+      <c r="Y205" s="7">
         <v>353492400.88999999</v>
       </c>
-      <c r="Z205" s="2">
+      <c r="Z205" s="7">
         <v>390492000</v>
       </c>
       <c r="AA205" s="3">
@@ -23061,32 +23069,32 @@
       <c r="X206" s="2">
         <v>1737552420</v>
       </c>
-      <c r="Y206" s="2">
+      <c r="Y206" s="7">
         <v>1885687953.98</v>
       </c>
-      <c r="Z206" s="2">
+      <c r="Z206" s="7">
         <v>2090678000</v>
       </c>
       <c r="AA206" s="3">
-        <v>2192118411.3490162</v>
+        <v>2183851266.4432659</v>
       </c>
       <c r="AB206" s="3">
-        <v>2295780500.9609947</v>
+        <v>2286827269.6007071</v>
       </c>
       <c r="AC206" s="3">
-        <v>2403111373.8084912</v>
+        <v>2397239225.2604203</v>
       </c>
       <c r="AD206" s="3">
-        <v>2516970236.6787882</v>
+        <v>2509817850.7137728</v>
       </c>
       <c r="AE206" s="3">
-        <v>2636656456.9576869</v>
+        <v>2626776975.6177936</v>
       </c>
       <c r="AF206" s="3">
-        <v>2761696111.1754422</v>
+        <v>2749893452.1388617</v>
       </c>
       <c r="AG206" s="3">
-        <v>2892447153.846035</v>
+        <v>2879237231.4092937</v>
       </c>
     </row>
     <row r="207" spans="1:33" x14ac:dyDescent="0.25">
@@ -23162,32 +23170,32 @@
       <c r="X207" s="2">
         <v>1357128329</v>
       </c>
-      <c r="Y207" s="2">
+      <c r="Y207" s="7">
         <v>1476160688.6300001</v>
       </c>
-      <c r="Z207" s="2">
+      <c r="Z207" s="7">
         <v>1314938000</v>
       </c>
       <c r="AA207" s="3">
-        <v>1367674914.7023046</v>
+        <v>1370738449.2681975</v>
       </c>
       <c r="AB207" s="3">
-        <v>1395205641.3352697</v>
+        <v>1398936517.8675334</v>
       </c>
       <c r="AC207" s="3">
-        <v>1411136075.1902745</v>
+        <v>1414375916.6069455</v>
       </c>
       <c r="AD207" s="3">
-        <v>1441629317.5437963</v>
+        <v>1445761878.4746156</v>
       </c>
       <c r="AE207" s="3">
-        <v>1476801172.4744134</v>
+        <v>1482256504.6941156</v>
       </c>
       <c r="AF207" s="3">
-        <v>1509762312.027667</v>
+        <v>1516301097.2108827</v>
       </c>
       <c r="AG207" s="3">
-        <v>1541522522.8455641</v>
+        <v>1548998826.8849423</v>
       </c>
     </row>
     <row r="208" spans="1:33" x14ac:dyDescent="0.25">
@@ -23263,32 +23271,32 @@
       <c r="X208" s="2">
         <v>848719071</v>
       </c>
-      <c r="Y208" s="2">
+      <c r="Y208" s="7">
         <v>891750304.01999998</v>
       </c>
-      <c r="Z208" s="2">
+      <c r="Z208" s="7">
         <v>912670000</v>
       </c>
       <c r="AA208" s="3">
-        <v>959654077.33619559</v>
+        <v>959140365.17501307</v>
       </c>
       <c r="AB208" s="3">
-        <v>991007936.45043778</v>
+        <v>992031604.53067267</v>
       </c>
       <c r="AC208" s="3">
-        <v>1015257986.8593704</v>
+        <v>1018858675.6437273</v>
       </c>
       <c r="AD208" s="3">
-        <v>1049842661.28286</v>
+        <v>1055052201.348099</v>
       </c>
       <c r="AE208" s="3">
-        <v>1088361477.1688297</v>
+        <v>1094979633.7747042</v>
       </c>
       <c r="AF208" s="3">
-        <v>1126164230.9569712</v>
+        <v>1134524491.0039697</v>
       </c>
       <c r="AG208" s="3">
-        <v>1163919970.9154892</v>
+        <v>1174286409.3004663</v>
       </c>
     </row>
     <row r="209" spans="1:33" x14ac:dyDescent="0.25">
@@ -23364,10 +23372,10 @@
       <c r="X209" s="2">
         <v>263532405</v>
       </c>
-      <c r="Y209" s="2">
+      <c r="Y209" s="7">
         <v>262721288.94</v>
       </c>
-      <c r="Z209" s="2">
+      <c r="Z209" s="7">
         <v>312294000</v>
       </c>
       <c r="AA209" s="3">
@@ -23465,10 +23473,10 @@
       <c r="X210" s="2">
         <v>89610625</v>
       </c>
-      <c r="Y210" s="2">
+      <c r="Y210" s="7">
         <v>89676599.680000007</v>
       </c>
-      <c r="Z210" s="2">
+      <c r="Z210" s="7">
         <v>88879000</v>
       </c>
       <c r="AA210" s="3">
@@ -23566,32 +23574,32 @@
       <c r="X211" s="2">
         <v>1162726278</v>
       </c>
-      <c r="Y211" s="2">
+      <c r="Y211" s="7">
         <v>1096750587.99</v>
       </c>
-      <c r="Z211" s="2">
+      <c r="Z211" s="7">
         <v>1091871000</v>
       </c>
       <c r="AA211" s="3">
-        <v>1174519316.8697791</v>
+        <v>1174379856.6626587</v>
       </c>
       <c r="AB211" s="3">
-        <v>1213681272.5125434</v>
+        <v>1217904614.4061091</v>
       </c>
       <c r="AC211" s="3">
-        <v>1231733366.7497373</v>
+        <v>1242591891.0084913</v>
       </c>
       <c r="AD211" s="3">
-        <v>1276666288.3504891</v>
+        <v>1292188067.6871789</v>
       </c>
       <c r="AE211" s="3">
-        <v>1330785159.9490125</v>
+        <v>1350708583.5266688</v>
       </c>
       <c r="AF211" s="3">
-        <v>1381335375.1465981</v>
+        <v>1406469278.8305249</v>
       </c>
       <c r="AG211" s="3">
-        <v>1430049296.2684989</v>
+        <v>1461054509.4594533</v>
       </c>
     </row>
     <row r="212" spans="1:33" x14ac:dyDescent="0.25">
@@ -23667,32 +23675,32 @@
       <c r="X212" s="2">
         <v>74055676</v>
       </c>
-      <c r="Y212" s="2">
+      <c r="Y212" s="7">
         <v>78613151.420000002</v>
       </c>
-      <c r="Z212" s="2">
+      <c r="Z212" s="7">
         <v>81283000</v>
       </c>
       <c r="AA212" s="3">
-        <v>81249054.031553984</v>
+        <v>81075930.966212615</v>
       </c>
       <c r="AB212" s="3">
-        <v>81344434.815282196</v>
+        <v>81149118.094661593</v>
       </c>
       <c r="AC212" s="3">
-        <v>81496386.221187219</v>
+        <v>81344469.421626002</v>
       </c>
       <c r="AD212" s="3">
-        <v>81582451.544694707</v>
+        <v>81397114.138572216</v>
       </c>
       <c r="AE212" s="3">
-        <v>81650484.355741099</v>
+        <v>81410593.964760408</v>
       </c>
       <c r="AF212" s="3">
-        <v>81732091.883817673</v>
+        <v>81453294.43669726</v>
       </c>
       <c r="AG212" s="3">
-        <v>81822133.700215682</v>
+        <v>81514062.713846013</v>
       </c>
     </row>
     <row r="213" spans="1:33" x14ac:dyDescent="0.25">
@@ -23768,10 +23776,10 @@
       <c r="X213" s="2">
         <v>160413441</v>
       </c>
-      <c r="Y213" s="2">
+      <c r="Y213" s="7">
         <v>173634126.28999999</v>
       </c>
-      <c r="Z213" s="2">
+      <c r="Z213" s="7">
         <v>134567000</v>
       </c>
       <c r="AA213" s="3">
@@ -23869,10 +23877,10 @@
       <c r="X214" s="2">
         <v>546048482</v>
       </c>
-      <c r="Y214" s="2">
+      <c r="Y214" s="7">
         <v>637005040.36000001</v>
       </c>
-      <c r="Z214" s="2">
+      <c r="Z214" s="7">
         <v>670409000</v>
       </c>
       <c r="AA214" s="3">
@@ -23970,10 +23978,10 @@
       <c r="X215" s="2">
         <v>195633086</v>
       </c>
-      <c r="Y215" s="2">
+      <c r="Y215" s="7">
         <v>182596198.66</v>
       </c>
-      <c r="Z215" s="2">
+      <c r="Z215" s="7">
         <v>227902000</v>
       </c>
       <c r="AA215" s="3">
@@ -24071,10 +24079,10 @@
       <c r="X216" s="2">
         <v>340027726</v>
       </c>
-      <c r="Y216" s="2">
+      <c r="Y216" s="7">
         <v>328755766.42000002</v>
       </c>
-      <c r="Z216" s="2">
+      <c r="Z216" s="7">
         <v>328940000</v>
       </c>
       <c r="AA216" s="3">
@@ -24172,32 +24180,32 @@
       <c r="X217" s="2">
         <v>251330640</v>
       </c>
-      <c r="Y217" s="2">
+      <c r="Y217" s="7">
         <v>263791697.83000001</v>
       </c>
-      <c r="Z217" s="2">
+      <c r="Z217" s="7">
         <v>265323000</v>
       </c>
       <c r="AA217" s="3">
-        <v>270878647.7527653</v>
+        <v>270853170.60778624</v>
       </c>
       <c r="AB217" s="3">
-        <v>274237000.89078236</v>
+        <v>274413180.45920485</v>
       </c>
       <c r="AC217" s="3">
-        <v>276615523.45966291</v>
+        <v>277098586.13720977</v>
       </c>
       <c r="AD217" s="3">
-        <v>280219974.17427289</v>
+        <v>280898687.98557496</v>
       </c>
       <c r="AE217" s="3">
-        <v>284205463.16476679</v>
+        <v>285052781.9477796</v>
       </c>
       <c r="AF217" s="3">
-        <v>287995125.00329185</v>
+        <v>289040003.22355729</v>
       </c>
       <c r="AG217" s="3">
-        <v>291677370.23066205</v>
+        <v>292940096.44310892</v>
       </c>
     </row>
     <row r="218" spans="1:33" x14ac:dyDescent="0.25">
@@ -24273,32 +24281,32 @@
       <c r="X218" s="2">
         <v>325918623</v>
       </c>
-      <c r="Y218" s="2">
+      <c r="Y218" s="7">
         <v>325113965.87</v>
       </c>
-      <c r="Z218" s="2">
+      <c r="Z218" s="7">
         <v>348708000</v>
       </c>
       <c r="AA218" s="3">
-        <v>355011080.4661777</v>
+        <v>353618294.91047043</v>
       </c>
       <c r="AB218" s="3">
-        <v>360391796.94132847</v>
+        <v>358981746.03725612</v>
       </c>
       <c r="AC218" s="3">
-        <v>365395294.21605211</v>
+        <v>364596552.04068768</v>
       </c>
       <c r="AD218" s="3">
-        <v>371012389.81563824</v>
+        <v>370097192.00889724</v>
       </c>
       <c r="AE218" s="3">
-        <v>376866999.87857634</v>
+        <v>375624721.77149844</v>
       </c>
       <c r="AF218" s="3">
-        <v>382699560.80362314</v>
+        <v>381277239.29184604</v>
       </c>
       <c r="AG218" s="3">
-        <v>388550657.06673795</v>
+        <v>387041404.3545962</v>
       </c>
     </row>
     <row r="219" spans="1:33" x14ac:dyDescent="0.25">
@@ -24374,32 +24382,32 @@
       <c r="X219" s="2">
         <v>4355653783</v>
       </c>
-      <c r="Y219" s="2">
+      <c r="Y219" s="7">
         <v>4718663670.4700003</v>
       </c>
-      <c r="Z219" s="2">
+      <c r="Z219" s="7">
         <v>4621903000</v>
       </c>
       <c r="AA219" s="3">
-        <v>4888533621.2486362</v>
+        <v>4888623826.0851574</v>
       </c>
       <c r="AB219" s="3">
-        <v>4973282694.5924845</v>
+        <v>4990739343.8975363</v>
       </c>
       <c r="AC219" s="3">
-        <v>4971984384.534173</v>
+        <v>5014852508.7963572</v>
       </c>
       <c r="AD219" s="3">
-        <v>5073038521.1319008</v>
+        <v>5133279215.4052505</v>
       </c>
       <c r="AE219" s="3">
-        <v>5204719556.1641779</v>
+        <v>5280883797.744771</v>
       </c>
       <c r="AF219" s="3">
-        <v>5317971469.4792528</v>
+        <v>5412506363.7747507</v>
       </c>
       <c r="AG219" s="3">
-        <v>5419908413.160099</v>
+        <v>5534613050.9688845</v>
       </c>
     </row>
     <row r="220" spans="1:33" x14ac:dyDescent="0.25">
@@ -24475,32 +24483,32 @@
       <c r="X220" s="2">
         <v>560640321</v>
       </c>
-      <c r="Y220" s="2">
+      <c r="Y220" s="7">
         <v>554612041.78999996</v>
       </c>
-      <c r="Z220" s="2">
+      <c r="Z220" s="7">
         <v>565977000</v>
       </c>
       <c r="AA220" s="3">
-        <v>582547578.83862245</v>
+        <v>581663072.65637779</v>
       </c>
       <c r="AB220" s="3">
-        <v>590112041.89418554</v>
+        <v>589994004.71616876</v>
       </c>
       <c r="AC220" s="3">
-        <v>593581898.71848965</v>
+        <v>594998480.84242094</v>
       </c>
       <c r="AD220" s="3">
-        <v>602005864.33155012</v>
+        <v>604110541.70117879</v>
       </c>
       <c r="AE220" s="3">
-        <v>611918414.10454881</v>
+        <v>614491414.59747922</v>
       </c>
       <c r="AF220" s="3">
-        <v>620957091.34896564</v>
+        <v>624194606.41898119</v>
       </c>
       <c r="AG220" s="3">
-        <v>629479647.34766674</v>
+        <v>633514242.40020478</v>
       </c>
     </row>
     <row r="221" spans="1:33" x14ac:dyDescent="0.25">
@@ -24576,10 +24584,10 @@
       <c r="X221" s="2">
         <v>357371984</v>
       </c>
-      <c r="Y221" s="2">
+      <c r="Y221" s="7">
         <v>345236995.60000002</v>
       </c>
-      <c r="Z221" s="2">
+      <c r="Z221" s="7">
         <v>373208000</v>
       </c>
       <c r="AA221" s="3">
@@ -24677,32 +24685,32 @@
       <c r="X222" s="2">
         <v>1905735664</v>
       </c>
-      <c r="Y222" s="2">
+      <c r="Y222" s="7">
         <v>1872568049.75</v>
       </c>
-      <c r="Z222" s="2">
+      <c r="Z222" s="7">
         <v>1731868000</v>
       </c>
       <c r="AA222" s="3">
-        <v>1757466982.1475861</v>
+        <v>1759839019.4756882</v>
       </c>
       <c r="AB222" s="3">
-        <v>1752495673.8483207</v>
+        <v>1755521242.5077946</v>
       </c>
       <c r="AC222" s="3">
-        <v>1734080071.6965694</v>
+        <v>1736971129.6042414</v>
       </c>
       <c r="AD222" s="3">
-        <v>1731436420.8304462</v>
+        <v>1735102658.506844</v>
       </c>
       <c r="AE222" s="3">
-        <v>1733052607.4821973</v>
+        <v>1737741860.8082647</v>
       </c>
       <c r="AF222" s="3">
-        <v>1731495642.1924899</v>
+        <v>1737022061.0557544</v>
       </c>
       <c r="AG222" s="3">
-        <v>1727982181.0706968</v>
+        <v>1734227495.819751</v>
       </c>
     </row>
     <row r="223" spans="1:33" x14ac:dyDescent="0.25">
@@ -24778,10 +24786,10 @@
       <c r="X223" s="2">
         <v>82697708</v>
       </c>
-      <c r="Y223" s="2">
+      <c r="Y223" s="7">
         <v>94665997.920000002</v>
       </c>
-      <c r="Z223" s="2">
+      <c r="Z223" s="7">
         <v>96784000</v>
       </c>
       <c r="AA223" s="3">
@@ -24879,10 +24887,10 @@
       <c r="X224" s="2">
         <v>174286487</v>
       </c>
-      <c r="Y224" s="2">
+      <c r="Y224" s="7">
         <v>185867683.75999999</v>
       </c>
-      <c r="Z224" s="2">
+      <c r="Z224" s="7">
         <v>198674000</v>
       </c>
       <c r="AA224" s="3">
@@ -24980,32 +24988,32 @@
       <c r="X225" s="2">
         <v>460405968</v>
       </c>
-      <c r="Y225" s="2">
+      <c r="Y225" s="7">
         <v>495764751.93000001</v>
       </c>
-      <c r="Z225" s="2">
+      <c r="Z225" s="7">
         <v>456660000</v>
       </c>
       <c r="AA225" s="3">
-        <v>474965996.30347466</v>
+        <v>476872289.6210466</v>
       </c>
       <c r="AB225" s="3">
-        <v>478792920.46383178</v>
+        <v>482181250.41704047</v>
       </c>
       <c r="AC225" s="3">
-        <v>475962969.645468</v>
+        <v>480583224.7283572</v>
       </c>
       <c r="AD225" s="3">
-        <v>480926931.72026062</v>
+        <v>487112571.21004146</v>
       </c>
       <c r="AE225" s="3">
-        <v>488092717.20506316</v>
+        <v>495983042.62560403</v>
       </c>
       <c r="AF225" s="3">
-        <v>493739040.53286612</v>
+        <v>503305835.3866806</v>
       </c>
       <c r="AG225" s="3">
-        <v>498435227.91014355</v>
+        <v>509666102.97909188</v>
       </c>
     </row>
     <row r="226" spans="1:33" x14ac:dyDescent="0.25">
@@ -25081,10 +25089,10 @@
       <c r="X226" s="2">
         <v>131404446</v>
       </c>
-      <c r="Y226" s="2">
+      <c r="Y226" s="7">
         <v>123588950.05</v>
       </c>
-      <c r="Z226" s="2">
+      <c r="Z226" s="7">
         <v>132525000</v>
       </c>
       <c r="AA226" s="3">
@@ -25182,32 +25190,32 @@
       <c r="X227" s="2">
         <v>375535359</v>
       </c>
-      <c r="Y227" s="2">
+      <c r="Y227" s="7">
         <v>376365406.37</v>
       </c>
-      <c r="Z227" s="2">
+      <c r="Z227" s="7">
         <v>383453000</v>
       </c>
       <c r="AA227" s="3">
-        <v>396453073.25666338</v>
+        <v>396313784.63380265</v>
       </c>
       <c r="AB227" s="3">
-        <v>405698634.70919716</v>
+        <v>405916273.56123334</v>
       </c>
       <c r="AC227" s="3">
-        <v>413287620.11423522</v>
+        <v>414103410.41432351</v>
       </c>
       <c r="AD227" s="3">
-        <v>423249660.45740205</v>
+        <v>424422446.80993778</v>
       </c>
       <c r="AE227" s="3">
-        <v>434076977.9233073</v>
+        <v>435550146.02149361</v>
       </c>
       <c r="AF227" s="3">
-        <v>444703454.33286744</v>
+        <v>446547789.51843643</v>
       </c>
       <c r="AG227" s="3">
-        <v>455287904.83701646</v>
+        <v>457556176.19005787</v>
       </c>
     </row>
     <row r="228" spans="1:33" x14ac:dyDescent="0.25">
@@ -25283,10 +25291,10 @@
       <c r="X228" s="2">
         <v>110509896</v>
       </c>
-      <c r="Y228" s="2">
+      <c r="Y228" s="7">
         <v>108625137.78</v>
       </c>
-      <c r="Z228" s="2">
+      <c r="Z228" s="7">
         <v>115351000</v>
       </c>
       <c r="AA228" s="3">
@@ -25384,10 +25392,10 @@
       <c r="X229" s="2">
         <v>315044676</v>
       </c>
-      <c r="Y229" s="2">
+      <c r="Y229" s="7">
         <v>336352711.38999999</v>
       </c>
-      <c r="Z229" s="2">
+      <c r="Z229" s="7">
         <v>347636000</v>
       </c>
       <c r="AA229" s="3">
@@ -25485,10 +25493,10 @@
       <c r="X230" s="2">
         <v>550828628</v>
       </c>
-      <c r="Y230" s="2">
+      <c r="Y230" s="7">
         <v>624467999.51999998</v>
       </c>
-      <c r="Z230" s="2">
+      <c r="Z230" s="7">
         <v>701076000</v>
       </c>
       <c r="AA230" s="3">
@@ -25586,10 +25594,10 @@
       <c r="X231" s="2">
         <v>781418155</v>
       </c>
-      <c r="Y231" s="2">
+      <c r="Y231" s="7">
         <v>743034683.10000002</v>
       </c>
-      <c r="Z231" s="2">
+      <c r="Z231" s="7">
         <v>672250000</v>
       </c>
       <c r="AA231" s="3">
@@ -25687,10 +25695,10 @@
       <c r="X232" s="2">
         <v>122292661</v>
       </c>
-      <c r="Y232" s="2">
+      <c r="Y232" s="7">
         <v>133575415.78</v>
       </c>
-      <c r="Z232" s="2">
+      <c r="Z232" s="7">
         <v>128409000</v>
       </c>
       <c r="AA232" s="3">
@@ -25788,10 +25796,10 @@
       <c r="X233" s="2">
         <v>85960010</v>
       </c>
-      <c r="Y233" s="2">
+      <c r="Y233" s="7">
         <v>97512387.159999996</v>
       </c>
-      <c r="Z233" s="2">
+      <c r="Z233" s="7">
         <v>108834000</v>
       </c>
       <c r="AA233" s="3">
@@ -25889,10 +25897,10 @@
       <c r="X234" s="2">
         <v>234987261</v>
       </c>
-      <c r="Y234" s="2">
+      <c r="Y234" s="7">
         <v>251128662.08000001</v>
       </c>
-      <c r="Z234" s="2">
+      <c r="Z234" s="7">
         <v>277594000</v>
       </c>
       <c r="AA234" s="3">
@@ -25990,32 +25998,32 @@
       <c r="X235" s="2">
         <v>317481960</v>
       </c>
-      <c r="Y235" s="2">
+      <c r="Y235" s="7">
         <v>294717421.14999998</v>
       </c>
-      <c r="Z235" s="2">
+      <c r="Z235" s="7">
         <v>342769000</v>
       </c>
       <c r="AA235" s="3">
-        <v>357424356.77530277</v>
+        <v>356815185.05878031</v>
       </c>
       <c r="AB235" s="3">
-        <v>361452038.49888045</v>
+        <v>361043751.22253025</v>
       </c>
       <c r="AC235" s="3">
-        <v>360561877.64234078</v>
+        <v>360736298.27327693</v>
       </c>
       <c r="AD235" s="3">
-        <v>365465702.87037486</v>
+        <v>365789494.11274707</v>
       </c>
       <c r="AE235" s="3">
-        <v>372042426.24022985</v>
+        <v>372400636.90911466</v>
       </c>
       <c r="AF235" s="3">
-        <v>377518913.62126905</v>
+        <v>378002907.37406045</v>
       </c>
       <c r="AG235" s="3">
-        <v>382312732.92222571</v>
+        <v>382982464.30259573</v>
       </c>
     </row>
     <row r="236" spans="1:33" x14ac:dyDescent="0.25">
@@ -26091,10 +26099,10 @@
       <c r="X236" s="2">
         <v>76858848</v>
       </c>
-      <c r="Y236" s="2">
+      <c r="Y236" s="7">
         <v>101080781.98999999</v>
       </c>
-      <c r="Z236" s="2">
+      <c r="Z236" s="7">
         <v>89006000</v>
       </c>
       <c r="AA236" s="3">
@@ -26192,10 +26200,10 @@
       <c r="X237" s="2">
         <v>57222480</v>
       </c>
-      <c r="Y237" s="2">
+      <c r="Y237" s="7">
         <v>57146906.450000003</v>
       </c>
-      <c r="Z237" s="2">
+      <c r="Z237" s="7">
         <v>62417000</v>
       </c>
       <c r="AA237" s="3">
@@ -26293,10 +26301,10 @@
       <c r="X238" s="2">
         <v>1483033836</v>
       </c>
-      <c r="Y238" s="2">
+      <c r="Y238" s="7">
         <v>1509364180.71</v>
       </c>
-      <c r="Z238" s="2">
+      <c r="Z238" s="7">
         <v>1749916000</v>
       </c>
       <c r="AA238" s="3">
@@ -26394,32 +26402,32 @@
       <c r="X239" s="2">
         <v>5544392318</v>
       </c>
-      <c r="Y239" s="2">
+      <c r="Y239" s="7">
         <v>5267020886.9399996</v>
       </c>
-      <c r="Z239" s="2">
+      <c r="Z239" s="7">
         <v>5038223000</v>
       </c>
       <c r="AA239" s="3">
-        <v>5267246765.3054686</v>
+        <v>5273456773.3395653</v>
       </c>
       <c r="AB239" s="3">
-        <v>5276633564.5093327</v>
+        <v>5287522249.4065685</v>
       </c>
       <c r="AC239" s="3">
-        <v>5185535837.7173185</v>
+        <v>5200115390.9340038</v>
       </c>
       <c r="AD239" s="3">
-        <v>5211549651.4282579</v>
+        <v>5230938851.8020277</v>
       </c>
       <c r="AE239" s="3">
-        <v>5269464298.9737949</v>
+        <v>5294087244.0458136</v>
       </c>
       <c r="AF239" s="3">
-        <v>5304082132.0390596</v>
+        <v>5333754344.4443197</v>
       </c>
       <c r="AG239" s="3">
-        <v>5324052364.9944334</v>
+        <v>5358641419.6802406</v>
       </c>
     </row>
     <row r="240" spans="1:33" x14ac:dyDescent="0.25">
@@ -26495,10 +26503,10 @@
       <c r="X240" s="2">
         <v>104058469</v>
       </c>
-      <c r="Y240" s="2">
+      <c r="Y240" s="7">
         <v>111566844.91</v>
       </c>
-      <c r="Z240" s="2">
+      <c r="Z240" s="7">
         <v>110781000</v>
       </c>
       <c r="AA240" s="3">
@@ -26596,10 +26604,10 @@
       <c r="X241" s="2">
         <v>132701577</v>
       </c>
-      <c r="Y241" s="2">
+      <c r="Y241" s="7">
         <v>250461436.88999999</v>
       </c>
-      <c r="Z241" s="2">
+      <c r="Z241" s="7">
         <v>265330000</v>
       </c>
       <c r="AA241" s="3">
@@ -26697,10 +26705,10 @@
       <c r="X242" s="2">
         <v>614720887</v>
       </c>
-      <c r="Y242" s="2">
+      <c r="Y242" s="7">
         <v>717785304.14999998</v>
       </c>
-      <c r="Z242" s="2">
+      <c r="Z242" s="7">
         <v>794990000</v>
       </c>
       <c r="AA242" s="3">
@@ -26798,10 +26806,10 @@
       <c r="X243" s="2">
         <v>259440364</v>
       </c>
-      <c r="Y243" s="2">
+      <c r="Y243" s="7">
         <v>206134238.12</v>
       </c>
-      <c r="Z243" s="2">
+      <c r="Z243" s="7">
         <v>197299000</v>
       </c>
       <c r="AA243" s="3">
@@ -26899,10 +26907,10 @@
       <c r="X244" s="2">
         <v>531132066</v>
       </c>
-      <c r="Y244" s="2">
+      <c r="Y244" s="7">
         <v>549218364.25</v>
       </c>
-      <c r="Z244" s="2">
+      <c r="Z244" s="7">
         <v>536174000</v>
       </c>
       <c r="AA244" s="3">
@@ -27000,32 +27008,32 @@
       <c r="X245" s="2">
         <v>10052015798</v>
       </c>
-      <c r="Y245" s="2">
+      <c r="Y245" s="7">
         <v>8470018440.2299995</v>
       </c>
-      <c r="Z245" s="2">
-        <v>8908625235.5323544</v>
+      <c r="Z245" s="7">
+        <v>7396332000</v>
       </c>
       <c r="AA245" s="3">
-        <v>10028801127.688427</v>
+        <v>8290841907.0140429</v>
       </c>
       <c r="AB245" s="3">
-        <v>10536119567.25514</v>
+        <v>8649760559.8929291</v>
       </c>
       <c r="AC245" s="3">
-        <v>10723786165.092331</v>
+        <v>8731317803.3296585</v>
       </c>
       <c r="AD245" s="3">
-        <v>11325947719.884342</v>
+        <v>9159514733.6790237</v>
       </c>
       <c r="AE245" s="3">
-        <v>12080730949.79937</v>
+        <v>9707983164.4220695</v>
       </c>
       <c r="AF245" s="3">
-        <v>12791369482.349569</v>
+        <v>10210879647.560249</v>
       </c>
       <c r="AG245" s="3">
-        <v>13482082341.581654</v>
+        <v>10688916510.499952</v>
       </c>
     </row>
     <row r="246" spans="1:33" x14ac:dyDescent="0.25">
@@ -27101,10 +27109,10 @@
       <c r="X246" s="2">
         <v>1215477846</v>
       </c>
-      <c r="Y246" s="2">
+      <c r="Y246" s="7">
         <v>1379255268.23</v>
       </c>
-      <c r="Z246" s="2">
+      <c r="Z246" s="7">
         <v>1303724000</v>
       </c>
       <c r="AA246" s="3">
@@ -27202,32 +27210,32 @@
       <c r="X247" s="2">
         <v>399115053</v>
       </c>
-      <c r="Y247" s="2">
+      <c r="Y247" s="7">
         <v>435272954.66000003</v>
       </c>
-      <c r="Z247" s="2">
+      <c r="Z247" s="7">
         <v>455830000</v>
       </c>
       <c r="AA247" s="3">
-        <v>483847397.59003597</v>
+        <v>483060864.43218338</v>
       </c>
       <c r="AB247" s="3">
-        <v>503536370.85268563</v>
+        <v>503549478.0050236</v>
       </c>
       <c r="AC247" s="3">
-        <v>519465219.78385109</v>
+        <v>521102630.48779571</v>
       </c>
       <c r="AD247" s="3">
-        <v>541402686.81730771</v>
+        <v>543873355.70474827</v>
       </c>
       <c r="AE247" s="3">
-        <v>565836305.2374841</v>
+        <v>568954292.12902904</v>
       </c>
       <c r="AF247" s="3">
-        <v>590149971.74207819</v>
+        <v>594166478.1478678</v>
       </c>
       <c r="AG247" s="3">
-        <v>614721237.69473028</v>
+        <v>619834910.03210735</v>
       </c>
     </row>
     <row r="248" spans="1:33" x14ac:dyDescent="0.25">
@@ -27303,10 +27311,10 @@
       <c r="X248" s="2">
         <v>416911360</v>
       </c>
-      <c r="Y248" s="2">
+      <c r="Y248" s="7">
         <v>446940082.86000001</v>
       </c>
-      <c r="Z248" s="2">
+      <c r="Z248" s="7">
         <v>463168000</v>
       </c>
       <c r="AA248" s="3">
@@ -27404,10 +27412,10 @@
       <c r="X249" s="2">
         <v>333925663</v>
       </c>
-      <c r="Y249" s="2">
+      <c r="Y249" s="7">
         <v>351818312.06999999</v>
       </c>
-      <c r="Z249" s="2">
+      <c r="Z249" s="7">
         <v>434705000</v>
       </c>
       <c r="AA249" s="3">
@@ -27505,10 +27513,10 @@
       <c r="X250" s="2">
         <v>1337706772</v>
       </c>
-      <c r="Y250" s="2">
+      <c r="Y250" s="7">
         <v>1299940927.77</v>
       </c>
-      <c r="Z250" s="2">
+      <c r="Z250" s="7">
         <v>1484851000</v>
       </c>
       <c r="AA250" s="3">
@@ -27606,10 +27614,10 @@
       <c r="X251" s="2">
         <v>16335346706</v>
       </c>
-      <c r="Y251" s="2">
+      <c r="Y251" s="7">
         <v>15850028663.299999</v>
       </c>
-      <c r="Z251" s="2">
+      <c r="Z251" s="7">
         <v>15575672000</v>
       </c>
       <c r="AA251" s="3">
@@ -27707,10 +27715,10 @@
       <c r="X252" s="2">
         <v>670636794</v>
       </c>
-      <c r="Y252" s="2">
+      <c r="Y252" s="7">
         <v>651102226.80999994</v>
       </c>
-      <c r="Z252" s="2">
+      <c r="Z252" s="7">
         <v>681891000</v>
       </c>
       <c r="AA252" s="3">
@@ -27808,10 +27816,10 @@
       <c r="X253" s="2">
         <v>376302543</v>
       </c>
-      <c r="Y253" s="2">
+      <c r="Y253" s="7">
         <v>317878571.5</v>
       </c>
-      <c r="Z253" s="2">
+      <c r="Z253" s="7">
         <v>355894000</v>
       </c>
       <c r="AA253" s="3">
@@ -27909,10 +27917,10 @@
       <c r="X254" s="2">
         <v>1640027997</v>
       </c>
-      <c r="Y254" s="2">
+      <c r="Y254" s="7">
         <v>1705837348.6400001</v>
       </c>
-      <c r="Z254" s="2">
+      <c r="Z254" s="7">
         <v>1843473000</v>
       </c>
       <c r="AA254" s="3">
@@ -28010,10 +28018,10 @@
       <c r="X255" s="2">
         <v>1096795671</v>
       </c>
-      <c r="Y255" s="2">
+      <c r="Y255" s="7">
         <v>1149282794.0999999</v>
       </c>
-      <c r="Z255" s="2">
+      <c r="Z255" s="7">
         <v>1241478000</v>
       </c>
       <c r="AA255" s="3">
@@ -28111,10 +28119,10 @@
       <c r="X256" s="2">
         <v>128964801</v>
       </c>
-      <c r="Y256" s="2">
+      <c r="Y256" s="7">
         <v>137024389.34999999</v>
       </c>
-      <c r="Z256" s="2">
+      <c r="Z256" s="7">
         <v>148541000</v>
       </c>
       <c r="AA256" s="3">
@@ -28212,10 +28220,10 @@
       <c r="X257" s="2">
         <v>59368234</v>
       </c>
-      <c r="Y257" s="2">
+      <c r="Y257" s="7">
         <v>57039536.880000003</v>
       </c>
-      <c r="Z257" s="2">
+      <c r="Z257" s="7">
         <v>73871000</v>
       </c>
       <c r="AA257" s="3">
@@ -28313,10 +28321,10 @@
       <c r="X258" s="2">
         <v>2566501751</v>
       </c>
-      <c r="Y258" s="2">
+      <c r="Y258" s="7">
         <v>2777351704.98</v>
       </c>
-      <c r="Z258" s="2">
+      <c r="Z258" s="7">
         <v>3105098000</v>
       </c>
       <c r="AA258" s="3">
@@ -28414,10 +28422,10 @@
       <c r="X259" s="2">
         <v>119373821</v>
       </c>
-      <c r="Y259" s="2">
+      <c r="Y259" s="7">
         <v>123653590.92</v>
       </c>
-      <c r="Z259" s="2">
+      <c r="Z259" s="7">
         <v>148311000</v>
       </c>
       <c r="AA259" s="3">
@@ -28515,10 +28523,10 @@
       <c r="X260" s="2">
         <v>622207422</v>
       </c>
-      <c r="Y260" s="2">
+      <c r="Y260" s="7">
         <v>668615518.60000002</v>
       </c>
-      <c r="Z260" s="2">
+      <c r="Z260" s="7">
         <v>718463000</v>
       </c>
       <c r="AA260" s="3">
@@ -28616,32 +28624,32 @@
       <c r="X261" s="2">
         <v>896423749</v>
       </c>
-      <c r="Y261" s="2">
+      <c r="Y261" s="7">
         <v>900087879.89999998</v>
       </c>
-      <c r="Z261" s="2">
+      <c r="Z261" s="7">
         <v>906591000</v>
       </c>
       <c r="AA261" s="3">
-        <v>947778590.21378684</v>
+        <v>948247758.27108335</v>
       </c>
       <c r="AB261" s="3">
-        <v>971354685.90250361</v>
+        <v>972229308.77111149</v>
       </c>
       <c r="AC261" s="3">
-        <v>986809603.14048874</v>
+        <v>988058540.20796561</v>
       </c>
       <c r="AD261" s="3">
-        <v>1012858872.4864517</v>
+        <v>1014558575.7080858</v>
       </c>
       <c r="AE261" s="3">
-        <v>1042501884.2363585</v>
+        <v>1044694812.2022744</v>
       </c>
       <c r="AF261" s="3">
-        <v>1070783244.5381342</v>
+        <v>1073481206.2997601</v>
       </c>
       <c r="AG261" s="3">
-        <v>1098418458.3745165</v>
+        <v>1101636823.5221643</v>
       </c>
     </row>
     <row r="262" spans="1:33" x14ac:dyDescent="0.25">
@@ -28717,10 +28725,10 @@
       <c r="X262" s="2">
         <v>1391133462</v>
       </c>
-      <c r="Y262" s="2">
+      <c r="Y262" s="7">
         <v>1429738687.6199999</v>
       </c>
-      <c r="Z262" s="2">
+      <c r="Z262" s="7">
         <v>1506648000</v>
       </c>
       <c r="AA262" s="3">
@@ -28818,10 +28826,10 @@
       <c r="X263" s="2">
         <v>139318243</v>
       </c>
-      <c r="Y263" s="2">
+      <c r="Y263" s="7">
         <v>137611635.16999999</v>
       </c>
-      <c r="Z263" s="2">
+      <c r="Z263" s="7">
         <v>147398000</v>
       </c>
       <c r="AA263" s="3">
@@ -28919,10 +28927,10 @@
       <c r="X264" s="2">
         <v>802069566</v>
       </c>
-      <c r="Y264" s="2">
+      <c r="Y264" s="7">
         <v>768926088.25999999</v>
       </c>
-      <c r="Z264" s="2">
+      <c r="Z264" s="7">
         <v>804482000</v>
       </c>
       <c r="AA264" s="3">
@@ -29020,10 +29028,10 @@
       <c r="X265" s="2">
         <v>1074513108</v>
       </c>
-      <c r="Y265" s="2">
+      <c r="Y265" s="7">
         <v>1180567876.8</v>
       </c>
-      <c r="Z265" s="2">
+      <c r="Z265" s="7">
         <v>1304359000</v>
       </c>
       <c r="AA265" s="3">
@@ -29121,10 +29129,10 @@
       <c r="X266" s="2">
         <v>98429700</v>
       </c>
-      <c r="Y266" s="2">
+      <c r="Y266" s="7">
         <v>105066603.42</v>
       </c>
-      <c r="Z266" s="2">
+      <c r="Z266" s="7">
         <v>123620000</v>
       </c>
       <c r="AA266" s="3">
@@ -29222,32 +29230,32 @@
       <c r="X267" s="2">
         <v>996959074</v>
       </c>
-      <c r="Y267" s="2">
+      <c r="Y267" s="7">
         <v>1025321337.37</v>
       </c>
-      <c r="Z267" s="2">
+      <c r="Z267" s="7">
         <v>1038273000</v>
       </c>
       <c r="AA267" s="3">
-        <v>1068178872.5496032</v>
+        <v>1067667186.1304102</v>
       </c>
       <c r="AB267" s="3">
-        <v>1086056822.3493974</v>
+        <v>1086637851.0343099</v>
       </c>
       <c r="AC267" s="3">
-        <v>1098518961.0738101</v>
+        <v>1100949836.5505717</v>
       </c>
       <c r="AD267" s="3">
-        <v>1117886381.0261307</v>
+        <v>1121371440.2161405</v>
       </c>
       <c r="AE267" s="3">
-        <v>1139478057.5288019</v>
+        <v>1143821930.5618198</v>
       </c>
       <c r="AF267" s="3">
-        <v>1160056486.6116991</v>
+        <v>1165467523.346981</v>
       </c>
       <c r="AG267" s="3">
-        <v>1180107721.2227974</v>
+        <v>1186733785.6145868</v>
       </c>
     </row>
     <row r="268" spans="1:33" x14ac:dyDescent="0.25">
@@ -29323,10 +29331,10 @@
       <c r="X268" s="2">
         <v>709198999</v>
       </c>
-      <c r="Y268" s="2">
+      <c r="Y268" s="7">
         <v>682456332.80999994</v>
       </c>
-      <c r="Z268" s="2">
+      <c r="Z268" s="7">
         <v>760285000</v>
       </c>
       <c r="AA268" s="3">
@@ -29424,10 +29432,10 @@
       <c r="X269" s="2">
         <v>77372271</v>
       </c>
-      <c r="Y269" s="2">
+      <c r="Y269" s="7">
         <v>86246251.450000003</v>
       </c>
-      <c r="Z269" s="2">
+      <c r="Z269" s="7">
         <v>88349000</v>
       </c>
       <c r="AA269" s="3">
@@ -29525,10 +29533,10 @@
       <c r="X270" s="2">
         <v>2877714048</v>
       </c>
-      <c r="Y270" s="2">
+      <c r="Y270" s="7">
         <v>3261270744.6300001</v>
       </c>
-      <c r="Z270" s="2">
+      <c r="Z270" s="7">
         <v>3687049000</v>
       </c>
       <c r="AA270" s="3">
@@ -29626,10 +29634,10 @@
       <c r="X271" s="2">
         <v>182808131</v>
       </c>
-      <c r="Y271" s="2">
+      <c r="Y271" s="7">
         <v>170968512.34999999</v>
       </c>
-      <c r="Z271" s="2">
+      <c r="Z271" s="7">
         <v>197892000</v>
       </c>
       <c r="AA271" s="3">
@@ -29727,32 +29735,32 @@
       <c r="X272" s="2">
         <v>2991711681</v>
       </c>
-      <c r="Y272" s="2">
+      <c r="Y272" s="7">
         <v>2842502026.9099998</v>
       </c>
-      <c r="Z272" s="2">
+      <c r="Z272" s="7">
         <v>2737817000</v>
       </c>
       <c r="AA272" s="3">
-        <v>2867653310.022099</v>
+        <v>2869181390.75037</v>
       </c>
       <c r="AB272" s="3">
-        <v>2889756775.8152695</v>
+        <v>2901422665.9983258</v>
       </c>
       <c r="AC272" s="3">
-        <v>2861980982.482553</v>
+        <v>2887533876.4210014</v>
       </c>
       <c r="AD272" s="3">
-        <v>2892458541.3715868</v>
+        <v>2927838995.3844881</v>
       </c>
       <c r="AE272" s="3">
-        <v>2939294850.3309102</v>
+        <v>2983722840.561492</v>
       </c>
       <c r="AF272" s="3">
-        <v>2974746357.0556316</v>
+        <v>3029268756.4384294</v>
       </c>
       <c r="AG272" s="3">
-        <v>3003039286.1218548</v>
+        <v>3068362633.4950285</v>
       </c>
     </row>
     <row r="273" spans="1:33" x14ac:dyDescent="0.25">
@@ -29828,32 +29836,32 @@
       <c r="X273" s="2">
         <v>357975109</v>
       </c>
-      <c r="Y273" s="2">
+      <c r="Y273" s="7">
         <v>303108681.81999999</v>
       </c>
-      <c r="Z273" s="2">
+      <c r="Z273" s="7">
         <v>304453000</v>
       </c>
       <c r="AA273" s="3">
-        <v>324606997.61090612</v>
+        <v>324843297.07157129</v>
       </c>
       <c r="AB273" s="3">
-        <v>329705233.10432398</v>
+        <v>330273222.92236191</v>
       </c>
       <c r="AC273" s="3">
-        <v>327623741.91150904</v>
+        <v>328555239.64514542</v>
       </c>
       <c r="AD273" s="3">
-        <v>333994445.62701547</v>
+        <v>335270101.55980569</v>
       </c>
       <c r="AE273" s="3">
-        <v>342842876.39507544</v>
+        <v>344474109.12556976</v>
       </c>
       <c r="AF273" s="3">
-        <v>350125013.94993532</v>
+        <v>352129877.07203859</v>
       </c>
       <c r="AG273" s="3">
-        <v>356426673.52049494</v>
+        <v>358819416.60526735</v>
       </c>
     </row>
     <row r="274" spans="1:33" x14ac:dyDescent="0.25">
@@ -29929,32 +29937,32 @@
       <c r="X274" s="2">
         <v>1797396309</v>
       </c>
-      <c r="Y274" s="2">
+      <c r="Y274" s="7">
         <v>1971388592.71</v>
       </c>
-      <c r="Z274" s="2">
+      <c r="Z274" s="7">
         <v>2060110000</v>
       </c>
       <c r="AA274" s="3">
-        <v>2181765460.6081514</v>
+        <v>2182102806.8646846</v>
       </c>
       <c r="AB274" s="3">
-        <v>2268016902.4905028</v>
+        <v>2269213094.5495477</v>
       </c>
       <c r="AC274" s="3">
-        <v>2338371459.3349738</v>
+        <v>2340705414.4167433</v>
       </c>
       <c r="AD274" s="3">
-        <v>2434194378.3559079</v>
+        <v>2437492157.3560362</v>
       </c>
       <c r="AE274" s="3">
-        <v>2540576154.8272958</v>
+        <v>2544846021.9215598</v>
       </c>
       <c r="AF274" s="3">
-        <v>2646448404.9821506</v>
+        <v>2651819863.8566847</v>
       </c>
       <c r="AG274" s="3">
-        <v>2753415532.5517359</v>
+        <v>2760004677.9863477</v>
       </c>
     </row>
     <row r="275" spans="1:33" x14ac:dyDescent="0.25">
@@ -30030,10 +30038,10 @@
       <c r="X275" s="2">
         <v>274128986</v>
       </c>
-      <c r="Y275" s="2">
+      <c r="Y275" s="7">
         <v>197168878.93000001</v>
       </c>
-      <c r="Z275" s="2">
+      <c r="Z275" s="7">
         <v>198900000</v>
       </c>
       <c r="AA275" s="3">
@@ -30131,10 +30139,10 @@
       <c r="X276" s="2">
         <v>235740282</v>
       </c>
-      <c r="Y276" s="2">
+      <c r="Y276" s="7">
         <v>251960228.44999999</v>
       </c>
-      <c r="Z276" s="2">
+      <c r="Z276" s="7">
         <v>255516000</v>
       </c>
       <c r="AA276" s="3">
@@ -30232,10 +30240,10 @@
       <c r="X277" s="2">
         <v>979082507</v>
       </c>
-      <c r="Y277" s="2">
+      <c r="Y277" s="7">
         <v>1077903941.4300001</v>
       </c>
-      <c r="Z277" s="2">
+      <c r="Z277" s="7">
         <v>1194854000</v>
       </c>
       <c r="AA277" s="3">
@@ -30333,32 +30341,32 @@
       <c r="X278" s="2">
         <v>516922639</v>
       </c>
-      <c r="Y278" s="2">
+      <c r="Y278" s="7">
         <v>455867095.77999997</v>
       </c>
-      <c r="Z278" s="2">
+      <c r="Z278" s="7">
         <v>433330000</v>
       </c>
       <c r="AA278" s="3">
-        <v>471100298.98386091</v>
+        <v>471376541.16943848</v>
       </c>
       <c r="AB278" s="3">
-        <v>480855296.26041412</v>
+        <v>483912365.00693566</v>
       </c>
       <c r="AC278" s="3">
-        <v>476876575.09087175</v>
+        <v>483865118.91117567</v>
       </c>
       <c r="AD278" s="3">
-        <v>489098184.80023819</v>
+        <v>498926343.29369432</v>
       </c>
       <c r="AE278" s="3">
-        <v>506169831.78974813</v>
+        <v>518718766.88117272</v>
       </c>
       <c r="AF278" s="3">
-        <v>520338211.37145638</v>
+        <v>535993734.67755616</v>
       </c>
       <c r="AG278" s="3">
-        <v>532682772.08115548</v>
+        <v>551737476.92228746</v>
       </c>
     </row>
     <row r="279" spans="1:33" x14ac:dyDescent="0.25">
@@ -30434,10 +30442,10 @@
       <c r="X279" s="2">
         <v>5686126601</v>
       </c>
-      <c r="Y279" s="2">
+      <c r="Y279" s="7">
         <v>5846789181.0100002</v>
       </c>
-      <c r="Z279" s="2">
+      <c r="Z279" s="7">
         <v>6007108000</v>
       </c>
       <c r="AA279" s="3">
@@ -30535,10 +30543,10 @@
       <c r="X280" s="2">
         <v>215184473</v>
       </c>
-      <c r="Y280" s="2">
+      <c r="Y280" s="7">
         <v>208482125.78</v>
       </c>
-      <c r="Z280" s="2">
+      <c r="Z280" s="7">
         <v>229506000</v>
       </c>
       <c r="AA280" s="3">
@@ -30636,10 +30644,10 @@
       <c r="X281" s="2">
         <v>870949701</v>
       </c>
-      <c r="Y281" s="2">
+      <c r="Y281" s="7">
         <v>898985698.38999999</v>
       </c>
-      <c r="Z281" s="2">
+      <c r="Z281" s="7">
         <v>992639000</v>
       </c>
       <c r="AA281" s="3">
@@ -30737,10 +30745,10 @@
       <c r="X282" s="2">
         <v>100479851</v>
       </c>
-      <c r="Y282" s="2">
+      <c r="Y282" s="7">
         <v>111990845.15000001</v>
       </c>
-      <c r="Z282" s="2">
+      <c r="Z282" s="7">
         <v>116753000</v>
       </c>
       <c r="AA282" s="3">
@@ -30838,10 +30846,10 @@
       <c r="X283" s="2">
         <v>420552533</v>
       </c>
-      <c r="Y283" s="2">
+      <c r="Y283" s="7">
         <v>426588071.07999998</v>
       </c>
-      <c r="Z283" s="2">
+      <c r="Z283" s="7">
         <v>471776000</v>
       </c>
       <c r="AA283" s="3">
@@ -30939,10 +30947,10 @@
       <c r="X284" s="2">
         <v>104406653</v>
       </c>
-      <c r="Y284" s="2">
+      <c r="Y284" s="7">
         <v>93319495.849999994</v>
       </c>
-      <c r="Z284" s="2">
+      <c r="Z284" s="7">
         <v>131850000</v>
       </c>
       <c r="AA284" s="3">
@@ -31040,10 +31048,10 @@
       <c r="X285" s="2">
         <v>1283783183</v>
       </c>
-      <c r="Y285" s="2">
+      <c r="Y285" s="7">
         <v>1401686743.74</v>
       </c>
-      <c r="Z285" s="2">
+      <c r="Z285" s="7">
         <v>1222447000</v>
       </c>
       <c r="AA285" s="3">
@@ -31141,10 +31149,10 @@
       <c r="X286" s="2">
         <v>237248683</v>
       </c>
-      <c r="Y286" s="2">
+      <c r="Y286" s="7">
         <v>282234065.08999997</v>
       </c>
-      <c r="Z286" s="2">
+      <c r="Z286" s="7">
         <v>301834000</v>
       </c>
       <c r="AA286" s="3">
@@ -31242,10 +31250,10 @@
       <c r="X287" s="2">
         <v>137085148</v>
       </c>
-      <c r="Y287" s="2">
+      <c r="Y287" s="7">
         <v>95036313.379999995</v>
       </c>
-      <c r="Z287" s="2">
+      <c r="Z287" s="7">
         <v>100064000</v>
       </c>
       <c r="AA287" s="3">
@@ -31343,10 +31351,10 @@
       <c r="X288" s="2">
         <v>637258391</v>
       </c>
-      <c r="Y288" s="2">
+      <c r="Y288" s="7">
         <v>656154074.70000005</v>
       </c>
-      <c r="Z288" s="2">
+      <c r="Z288" s="7">
         <v>661591000</v>
       </c>
       <c r="AA288" s="3">
@@ -31444,32 +31452,32 @@
       <c r="X289" s="2">
         <v>418822238</v>
       </c>
-      <c r="Y289" s="2">
+      <c r="Y289" s="7">
         <v>394782574.64999998</v>
       </c>
-      <c r="Z289" s="2">
+      <c r="Z289" s="7">
         <v>401953000</v>
       </c>
       <c r="AA289" s="3">
-        <v>412389923.53162777</v>
+        <v>412277875.88253564</v>
       </c>
       <c r="AB289" s="3">
-        <v>420544401.69310176</v>
+        <v>420647696.31613922</v>
       </c>
       <c r="AC289" s="3">
-        <v>427724562.68963295</v>
+        <v>428199533.26031107</v>
       </c>
       <c r="AD289" s="3">
-        <v>436378398.94676262</v>
+        <v>437063364.86873025</v>
       </c>
       <c r="AE289" s="3">
-        <v>445584461.69917119</v>
+        <v>446439213.91643417</v>
       </c>
       <c r="AF289" s="3">
-        <v>454697741.98913425</v>
+        <v>455766095.96643227</v>
       </c>
       <c r="AG289" s="3">
-        <v>463816629.22717923</v>
+        <v>465130227.42669976</v>
       </c>
     </row>
     <row r="290" spans="1:33" x14ac:dyDescent="0.25">
@@ -31545,10 +31553,10 @@
       <c r="X290" s="2">
         <v>4079178395</v>
       </c>
-      <c r="Y290" s="2">
+      <c r="Y290" s="7">
         <v>4214300587.98</v>
       </c>
-      <c r="Z290" s="2">
+      <c r="Z290" s="7">
         <v>4129523000</v>
       </c>
       <c r="AA290" s="3">
@@ -31646,10 +31654,10 @@
       <c r="X291" s="2">
         <v>167940106</v>
       </c>
-      <c r="Y291" s="2">
+      <c r="Y291" s="7">
         <v>179653395.91999999</v>
       </c>
-      <c r="Z291" s="2">
+      <c r="Z291" s="7">
         <v>193745000</v>
       </c>
       <c r="AA291" s="3">
@@ -31747,32 +31755,32 @@
       <c r="X292" s="2">
         <v>206795022</v>
       </c>
-      <c r="Y292" s="2">
+      <c r="Y292" s="7">
         <v>206877060.25</v>
       </c>
-      <c r="Z292" s="2">
+      <c r="Z292" s="7">
         <v>197839000</v>
       </c>
       <c r="AA292" s="3">
-        <v>207357253.12696886</v>
+        <v>207909932.79170376</v>
       </c>
       <c r="AB292" s="3">
-        <v>211713782.99873295</v>
+        <v>212809681.18394232</v>
       </c>
       <c r="AC292" s="3">
-        <v>213659654.72746906</v>
+        <v>215287795.91086245</v>
       </c>
       <c r="AD292" s="3">
-        <v>218577427.82351854</v>
+        <v>220797288.55009159</v>
       </c>
       <c r="AE292" s="3">
-        <v>224435222.97237638</v>
+        <v>227290297.82572478</v>
       </c>
       <c r="AF292" s="3">
-        <v>229817283.83392438</v>
+        <v>233327881.92471987</v>
       </c>
       <c r="AG292" s="3">
-        <v>234928476.86655387</v>
+        <v>239116257.00160199</v>
       </c>
     </row>
     <row r="293" spans="1:33" x14ac:dyDescent="0.25">
@@ -31848,10 +31856,10 @@
       <c r="X293" s="2">
         <v>3115919941</v>
       </c>
-      <c r="Y293" s="2">
+      <c r="Y293" s="7">
         <v>3161843234.9099998</v>
       </c>
-      <c r="Z293" s="2">
+      <c r="Z293" s="7">
         <v>3145565000</v>
       </c>
       <c r="AA293" s="3">
@@ -31949,10 +31957,10 @@
       <c r="X294" s="2">
         <v>250078359</v>
       </c>
-      <c r="Y294" s="2">
+      <c r="Y294" s="7">
         <v>223626713.34999999</v>
       </c>
-      <c r="Z294" s="2">
+      <c r="Z294" s="7">
         <v>249450000</v>
       </c>
       <c r="AA294" s="3">
@@ -32050,10 +32058,10 @@
       <c r="X295" s="2">
         <v>1737284496</v>
       </c>
-      <c r="Y295" s="2">
+      <c r="Y295" s="7">
         <v>1712802127.8599999</v>
       </c>
-      <c r="Z295" s="2">
+      <c r="Z295" s="7">
         <v>1737477000</v>
       </c>
       <c r="AA295" s="3">
@@ -32151,10 +32159,10 @@
       <c r="X296" s="2">
         <v>122344594</v>
       </c>
-      <c r="Y296" s="2">
+      <c r="Y296" s="7">
         <v>153584502.28999999</v>
       </c>
-      <c r="Z296" s="2">
+      <c r="Z296" s="7">
         <v>135060000</v>
       </c>
       <c r="AA296" s="3">
@@ -32193,120 +32201,120 @@
         <v>616</v>
       </c>
       <c r="E297" s="5">
-        <f>SUM(E2:E296)</f>
+        <f t="shared" ref="E297:AG297" si="1">SUM(E2:E296)</f>
         <v>302425135015</v>
       </c>
       <c r="F297" s="5">
-        <f>SUM(F2:F296)</f>
+        <f t="shared" si="1"/>
         <v>310558754291</v>
       </c>
       <c r="G297" s="5">
-        <f>SUM(G2:G296)</f>
+        <f t="shared" si="1"/>
         <v>331005528845</v>
       </c>
       <c r="H297" s="5">
-        <f>SUM(H2:H296)</f>
+        <f t="shared" si="1"/>
         <v>341992660193</v>
       </c>
       <c r="I297" s="5">
-        <f>SUM(I2:I296)</f>
+        <f t="shared" si="1"/>
         <v>348651317761</v>
       </c>
       <c r="J297" s="5">
-        <f>SUM(J2:J296)</f>
+        <f t="shared" si="1"/>
         <v>369958948008</v>
       </c>
       <c r="K297" s="5">
-        <f>SUM(K2:K296)</f>
+        <f t="shared" si="1"/>
         <v>377545563454</v>
       </c>
       <c r="L297" s="5">
-        <f>SUM(L2:L296)</f>
+        <f t="shared" si="1"/>
         <v>374349220884</v>
       </c>
       <c r="M297" s="5">
-        <f>SUM(M2:M296)</f>
+        <f t="shared" si="1"/>
         <v>399481458027</v>
       </c>
       <c r="N297" s="5">
-        <f>SUM(N2:N296)</f>
+        <f t="shared" si="1"/>
         <v>414992864205</v>
       </c>
       <c r="O297" s="5">
-        <f>SUM(O2:O296)</f>
+        <f t="shared" si="1"/>
         <v>420574532563</v>
       </c>
       <c r="P297" s="5">
-        <f>SUM(P2:P296)</f>
+        <f t="shared" si="1"/>
         <v>435779698481</v>
       </c>
       <c r="Q297" s="5">
-        <f>SUM(Q2:Q296)</f>
+        <f t="shared" si="1"/>
         <v>445572342640</v>
       </c>
       <c r="R297" s="5">
-        <f>SUM(R2:R296)</f>
+        <f t="shared" si="1"/>
         <v>430296409395</v>
       </c>
       <c r="S297" s="5">
-        <f>SUM(S2:S296)</f>
+        <f t="shared" si="1"/>
         <v>421306597311</v>
       </c>
       <c r="T297" s="5">
-        <f>SUM(T2:T296)</f>
+        <f t="shared" si="1"/>
         <v>439122382713</v>
       </c>
       <c r="U297" s="5">
-        <f>SUM(U2:U296)</f>
+        <f t="shared" si="1"/>
         <v>461049595037</v>
       </c>
       <c r="V297" s="5">
-        <f>SUM(V2:V296)</f>
+        <f t="shared" si="1"/>
         <v>478130019279</v>
       </c>
       <c r="W297" s="5">
-        <f>SUM(W2:W296)</f>
+        <f t="shared" si="1"/>
         <v>466109981337</v>
       </c>
       <c r="X297" s="5">
-        <f>SUM(X2:X296)</f>
+        <f t="shared" si="1"/>
         <v>505834938787</v>
       </c>
       <c r="Y297" s="5">
-        <f>SUM(Y2:Y296)</f>
+        <f t="shared" si="1"/>
         <v>510853581829.50989</v>
       </c>
       <c r="Z297" s="5">
-        <f>SUM(Z2:Z296)</f>
-        <v>527187560295.20911</v>
+        <f t="shared" si="1"/>
+        <v>513392972000</v>
       </c>
       <c r="AA297" s="6">
-        <f>SUM(AA2:AA296)</f>
-        <v>558906394419.16638</v>
+        <f t="shared" si="1"/>
+        <v>543501951353.02051</v>
       </c>
       <c r="AB297" s="6">
-        <f>SUM(AB2:AB296)</f>
-        <v>576597286126.80945</v>
+        <f t="shared" si="1"/>
+        <v>560087449245.32104</v>
       </c>
       <c r="AC297" s="6">
-        <f>SUM(AC2:AC296)</f>
-        <v>587827429378.01245</v>
+        <f t="shared" si="1"/>
+        <v>570412871430.1521</v>
       </c>
       <c r="AD297" s="6">
-        <f>SUM(AD2:AD296)</f>
-        <v>608602144157.75439</v>
+        <f t="shared" si="1"/>
+        <v>589808586340.64319</v>
       </c>
       <c r="AE297" s="6">
-        <f>SUM(AE2:AE296)</f>
-        <v>633109280042.0946</v>
+        <f t="shared" si="1"/>
+        <v>612688589683.00037</v>
       </c>
       <c r="AF297" s="6">
-        <f>SUM(AF2:AF296)</f>
-        <v>657181391824.74951</v>
+        <f t="shared" si="1"/>
+        <v>635056642116.14941</v>
       </c>
       <c r="AG297" s="6">
-        <f>SUM(AG2:AG296)</f>
-        <v>681473804086.19446</v>
+        <f t="shared" si="1"/>
+        <v>657533287733.8291</v>
       </c>
     </row>
   </sheetData>
